--- a/odoo-v19ce-erd-欄位中英對照表.xlsx
+++ b/odoo-v19ce-erd-欄位中英對照表.xlsx
@@ -13,9 +13,9 @@
     <sheet name="翻譯疑義" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'欄位對照'!$A$1:$G$108</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'實體對照'!$A$1:$D$25</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'翻譯疑義'!$A$1:$E$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'欄位對照'!$A$1:$H$137</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'實體對照'!$A$1:$E$28</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'翻譯疑義'!$A$1:$E$16</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -478,7 +478,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B19"/>
+  <dimension ref="A1:B20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -529,7 +529,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>index.html 的 mermaid erDiagram 區塊（第 276–481 行）</t>
+          <t>index.html 的四張視圖：總覽 / 聯絡人 / 商品主檔 / 採購</t>
         </is>
       </c>
     </row>
@@ -541,67 +541,67 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>24 個實體、107 條屬性行（其中 101 條為 model 欄位、6 條為中介表欄位）</t>
+          <t>27 個正典實體、136 條屬性行（128 條 model 欄位、8 條中介表欄位）</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
+      <c r="A7" s="2" t="inlineStr"/>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>邊界節點（在別的視圖已有完整定義）只列主鍵，不計入本表</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>翻譯覆蓋</t>
         </is>
       </c>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>101 條 model 欄位中 99 條有官方 zh_TW；2 條無翻譯，已於「欄位對照」標示</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr"/>
-      <c r="B8" s="3" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>128 條 model 欄位中 126 條有官方 zh_TW</t>
+        </is>
+      </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="inlineStr">
+      <c r="A9" s="2" t="inlineStr"/>
+      <c r="B9" s="3" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>欄位對照的三種名稱</t>
         </is>
       </c>
-      <c r="B9" s="3" t="inlineStr">
+      <c r="B10" s="3" t="inlineStr">
         <is>
           <t>「英文（欄位名）」＝資料庫技術欄位名，與 ERD 圖上一致。</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr"/>
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>「英文標籤 (en_US)」與「繁體中文 (zh_TW)」＝同一個標籤的兩種語言，互為譯文。</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr"/>
-      <c r="B11" s="3" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>「英文標籤 (en_US)」與「繁體中文 (zh_TW)」＝同一個標籤的兩種語言，互為譯文。</t>
+        </is>
+      </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="inlineStr">
+      <c r="A12" s="2" t="inlineStr"/>
+      <c r="B12" s="3" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
         <is>
           <t>「繁體中文」欄的性質</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B13" s="3" t="inlineStr">
         <is>
           <t>Odoo 官方 zh_TW 語言包的原始標籤，未經改寫。</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr"/>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>它是使用者在 Odoo 介面切換繁中時實際會看到的字，屬實查事實。</t>
         </is>
       </c>
     </row>
@@ -609,45 +609,53 @@
       <c r="A14" s="2" t="inlineStr"/>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>該語言包含誤譯與中國用語，未修正；疑義集中列於「翻譯疑義」分頁。</t>
+          <t>它是使用者在 Odoo 介面切換繁中時實際會看到的字，屬實查事實。</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr"/>
-      <c r="B15" s="3" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>該語言包含誤譯與中國用語，未修正；疑義集中列於「翻譯疑義」分頁。</t>
+        </is>
+      </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="inlineStr">
+      <c r="A16" s="2" t="inlineStr"/>
+      <c r="B16" s="3" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
         <is>
           <t>「翻譯疑義」分頁的性質</t>
         </is>
       </c>
-      <c r="B16" s="3" t="inlineStr">
+      <c r="B17" s="3" t="inlineStr">
         <is>
           <t>該分頁的「疑義」欄是編製者對照同庫其他欄位後的判讀，</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr"/>
-      <c r="B17" s="3" t="inlineStr">
-        <is>
-          <t>非 Odoo 官方立場，亦非系統事實。使用前請自行覆核。</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr"/>
-      <c r="B18" s="3" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>非 Odoo 官方立場，亦非系統事實。使用前請自行覆核。</t>
+        </is>
+      </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="inlineStr">
+      <c r="A19" s="2" t="inlineStr"/>
+      <c r="B19" s="3" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
         <is>
           <t>「備註」欄來源</t>
         </is>
       </c>
-      <c r="B19" s="3" t="inlineStr">
+      <c r="B20" s="3" t="inlineStr">
         <is>
           <t>沿用 index.html 圖上既有備註，內容為實查所得的約束與結構特性。</t>
         </is>
@@ -664,50 +672,56 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G108"/>
+  <dimension ref="A1:H137"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="34" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="8" customWidth="1" min="3" max="3"/>
-    <col width="36" customWidth="1" min="4" max="4"/>
-    <col width="26" customWidth="1" min="5" max="5"/>
-    <col width="22" customWidth="1" min="6" max="6"/>
-    <col width="40" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="34" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="8" customWidth="1" min="4" max="4"/>
+    <col width="36" customWidth="1" min="5" max="5"/>
+    <col width="26" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
+          <t>視圖</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
           <t>實體 (model)</t>
         </is>
       </c>
-      <c r="B1" s="4" t="inlineStr">
+      <c r="C1" s="4" t="inlineStr">
         <is>
           <t>欄位屬性</t>
         </is>
       </c>
-      <c r="C1" s="4" t="inlineStr">
+      <c r="D1" s="4" t="inlineStr">
         <is>
           <t>KEY</t>
         </is>
       </c>
-      <c r="D1" s="4" t="inlineStr">
+      <c r="E1" s="4" t="inlineStr">
         <is>
           <t>英文（欄位名）</t>
         </is>
       </c>
-      <c r="E1" s="4" t="inlineStr">
+      <c r="F1" s="4" t="inlineStr">
         <is>
           <t>英文標籤 (en_US)</t>
         </is>
       </c>
-      <c r="F1" s="4" t="inlineStr">
+      <c r="G1" s="4" t="inlineStr">
         <is>
           <t>繁體中文 (zh_TW)</t>
         </is>
       </c>
-      <c r="G1" s="4" t="inlineStr">
+      <c r="H1" s="4" t="inlineStr">
         <is>
           <t>備註</t>
         </is>
@@ -716,707 +730,836 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
+          <t>聯絡人</t>
+        </is>
+      </c>
+      <c r="B2" s="5" t="inlineStr">
+        <is>
           <t>res.partner</t>
         </is>
       </c>
-      <c r="B2" s="5" t="inlineStr">
+      <c r="C2" s="5" t="inlineStr">
         <is>
           <t>integer</t>
         </is>
       </c>
-      <c r="C2" s="5" t="inlineStr">
+      <c r="D2" s="5" t="inlineStr">
         <is>
           <t>PK</t>
         </is>
       </c>
-      <c r="D2" s="5" t="inlineStr">
+      <c r="E2" s="5" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="E2" s="5" t="inlineStr">
+      <c r="F2" s="5" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="F2" s="5" t="inlineStr">
+      <c r="G2" s="5" t="inlineStr">
         <is>
           <t>識別號</t>
         </is>
       </c>
-      <c r="G2" s="6" t="inlineStr"/>
+      <c r="H2" s="6" t="inlineStr">
+        <is>
+          <t>識別號</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="7" t="inlineStr">
         <is>
+          <t>聯絡人</t>
+        </is>
+      </c>
+      <c r="B3" s="7" t="inlineStr">
+        <is>
           <t>res.partner</t>
         </is>
       </c>
-      <c r="B3" s="7" t="inlineStr">
+      <c r="C3" s="7" t="inlineStr">
         <is>
           <t>char</t>
         </is>
       </c>
-      <c r="C3" s="7" t="inlineStr"/>
-      <c r="D3" s="7" t="inlineStr">
+      <c r="D3" s="7" t="inlineStr"/>
+      <c r="E3" s="7" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="E3" s="7" t="inlineStr">
+      <c r="F3" s="7" t="inlineStr">
         <is>
           <t>Name</t>
         </is>
       </c>
-      <c r="F3" s="7" t="inlineStr">
+      <c r="G3" s="7" t="inlineStr">
         <is>
           <t>名稱</t>
         </is>
       </c>
-      <c r="G3" s="8" t="inlineStr">
-        <is>
-          <t>CHECK 條件式必填</t>
+      <c r="H3" s="8" t="inlineStr">
+        <is>
+          <t>名稱 · CHECK 條件式必填</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
+          <t>聯絡人</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
           <t>res.partner</t>
         </is>
       </c>
-      <c r="B4" s="5" t="inlineStr">
+      <c r="C4" s="5" t="inlineStr">
         <is>
           <t>selection</t>
         </is>
       </c>
-      <c r="C4" s="5" t="inlineStr"/>
-      <c r="D4" s="5" t="inlineStr">
+      <c r="D4" s="5" t="inlineStr"/>
+      <c r="E4" s="5" t="inlineStr">
         <is>
           <t>type</t>
         </is>
       </c>
-      <c r="E4" s="5" t="inlineStr">
+      <c r="F4" s="5" t="inlineStr">
         <is>
           <t>Address Type</t>
         </is>
       </c>
-      <c r="F4" s="5" t="inlineStr">
+      <c r="G4" s="5" t="inlineStr">
         <is>
           <t>地址類型</t>
         </is>
       </c>
-      <c r="G4" s="6" t="inlineStr">
-        <is>
-          <t>contact invoice delivery other</t>
+      <c r="H4" s="6" t="inlineStr">
+        <is>
+          <t>地址類型 · contact invoice delivery other</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="7" t="inlineStr">
         <is>
+          <t>聯絡人</t>
+        </is>
+      </c>
+      <c r="B5" s="7" t="inlineStr">
+        <is>
           <t>res.partner</t>
         </is>
       </c>
-      <c r="B5" s="7" t="inlineStr">
+      <c r="C5" s="7" t="inlineStr">
         <is>
           <t>boolean</t>
         </is>
       </c>
-      <c r="C5" s="7" t="inlineStr"/>
-      <c r="D5" s="7" t="inlineStr">
+      <c r="D5" s="7" t="inlineStr"/>
+      <c r="E5" s="7" t="inlineStr">
         <is>
           <t>is_company</t>
         </is>
       </c>
-      <c r="E5" s="7" t="inlineStr">
+      <c r="F5" s="7" t="inlineStr">
         <is>
           <t>Is a Company</t>
         </is>
       </c>
-      <c r="F5" s="7" t="inlineStr">
+      <c r="G5" s="7" t="inlineStr">
         <is>
           <t>公司</t>
         </is>
       </c>
-      <c r="G5" s="8" t="inlineStr"/>
+      <c r="H5" s="8" t="inlineStr">
+        <is>
+          <t>公司</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
+          <t>聯絡人</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
           <t>res.partner</t>
         </is>
       </c>
-      <c r="B6" s="5" t="inlineStr">
+      <c r="C6" s="5" t="inlineStr">
         <is>
           <t>many2one</t>
         </is>
       </c>
-      <c r="C6" s="5" t="inlineStr">
+      <c r="D6" s="5" t="inlineStr">
         <is>
           <t>FK</t>
         </is>
       </c>
-      <c r="D6" s="5" t="inlineStr">
+      <c r="E6" s="5" t="inlineStr">
         <is>
           <t>parent_id</t>
         </is>
       </c>
-      <c r="E6" s="5" t="inlineStr">
+      <c r="F6" s="5" t="inlineStr">
         <is>
           <t>Related Company</t>
         </is>
       </c>
-      <c r="F6" s="5" t="inlineStr">
+      <c r="G6" s="5" t="inlineStr">
         <is>
           <t>關聯公司</t>
         </is>
       </c>
-      <c r="G6" s="6" t="inlineStr">
-        <is>
-          <t>自身 set-null</t>
+      <c r="H6" s="6" t="inlineStr">
+        <is>
+          <t>關聯公司 · 自身 set-null</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="7" t="inlineStr">
         <is>
+          <t>聯絡人</t>
+        </is>
+      </c>
+      <c r="B7" s="7" t="inlineStr">
+        <is>
           <t>res.partner</t>
         </is>
       </c>
-      <c r="B7" s="7" t="inlineStr">
+      <c r="C7" s="7" t="inlineStr">
         <is>
           <t>integer</t>
         </is>
       </c>
-      <c r="C7" s="7" t="inlineStr"/>
-      <c r="D7" s="7" t="inlineStr">
+      <c r="D7" s="7" t="inlineStr"/>
+      <c r="E7" s="7" t="inlineStr">
         <is>
           <t>customer_rank</t>
         </is>
       </c>
-      <c r="E7" s="7" t="inlineStr">
+      <c r="F7" s="7" t="inlineStr">
         <is>
           <t>Customer Rank</t>
         </is>
       </c>
-      <c r="F7" s="7" t="inlineStr">
+      <c r="G7" s="7" t="inlineStr">
         <is>
           <t>客戶評級</t>
         </is>
       </c>
-      <c r="G7" s="8" t="inlineStr">
-        <is>
-          <t>整數非布林</t>
+      <c r="H7" s="8" t="inlineStr">
+        <is>
+          <t>客戶評級 · 整數非布林</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
+          <t>聯絡人</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
           <t>res.partner</t>
         </is>
       </c>
-      <c r="B8" s="5" t="inlineStr">
+      <c r="C8" s="5" t="inlineStr">
         <is>
           <t>integer</t>
         </is>
       </c>
-      <c r="C8" s="5" t="inlineStr"/>
-      <c r="D8" s="5" t="inlineStr">
+      <c r="D8" s="5" t="inlineStr"/>
+      <c r="E8" s="5" t="inlineStr">
         <is>
           <t>supplier_rank</t>
         </is>
       </c>
-      <c r="E8" s="5" t="inlineStr">
+      <c r="F8" s="5" t="inlineStr">
         <is>
           <t>Supplier Rank</t>
         </is>
       </c>
-      <c r="F8" s="5" t="inlineStr">
+      <c r="G8" s="5" t="inlineStr">
         <is>
           <t>供應商排名</t>
         </is>
       </c>
-      <c r="G8" s="6" t="inlineStr">
-        <is>
-          <t>整數非布林</t>
+      <c r="H8" s="6" t="inlineStr">
+        <is>
+          <t>供應商排名 · 整數非布林</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="7" t="inlineStr">
         <is>
+          <t>聯絡人</t>
+        </is>
+      </c>
+      <c r="B9" s="7" t="inlineStr">
+        <is>
           <t>res.partner</t>
         </is>
       </c>
-      <c r="B9" s="7" t="inlineStr">
+      <c r="C9" s="7" t="inlineStr">
         <is>
           <t>char</t>
         </is>
       </c>
-      <c r="C9" s="7" t="inlineStr"/>
-      <c r="D9" s="7" t="inlineStr">
+      <c r="D9" s="7" t="inlineStr"/>
+      <c r="E9" s="7" t="inlineStr">
         <is>
           <t>vat</t>
         </is>
       </c>
-      <c r="E9" s="7" t="inlineStr">
+      <c r="F9" s="7" t="inlineStr">
         <is>
           <t>Tax ID</t>
         </is>
       </c>
-      <c r="F9" s="7" t="inlineStr">
+      <c r="G9" s="7" t="inlineStr">
         <is>
           <t>稅務編號</t>
         </is>
       </c>
-      <c r="G9" s="8" t="inlineStr">
-        <is>
-          <t>統一編號</t>
+      <c r="H9" s="8" t="inlineStr">
+        <is>
+          <t>稅務編號 · 統一編號</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
+          <t>聯絡人</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
           <t>res.partner</t>
         </is>
       </c>
-      <c r="B10" s="5" t="inlineStr">
+      <c r="C10" s="5" t="inlineStr">
         <is>
           <t>char</t>
         </is>
       </c>
-      <c r="C10" s="5" t="inlineStr"/>
-      <c r="D10" s="5" t="inlineStr">
+      <c r="D10" s="5" t="inlineStr"/>
+      <c r="E10" s="5" t="inlineStr">
         <is>
           <t>email</t>
         </is>
       </c>
-      <c r="E10" s="5" t="inlineStr">
+      <c r="F10" s="5" t="inlineStr">
         <is>
           <t>Email</t>
         </is>
       </c>
-      <c r="F10" s="5" t="inlineStr">
+      <c r="G10" s="5" t="inlineStr">
         <is>
           <t>電郵</t>
         </is>
       </c>
-      <c r="G10" s="6" t="inlineStr"/>
+      <c r="H10" s="6" t="inlineStr">
+        <is>
+          <t>電郵</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="7" t="inlineStr">
         <is>
+          <t>聯絡人</t>
+        </is>
+      </c>
+      <c r="B11" s="7" t="inlineStr">
+        <is>
           <t>res.partner</t>
         </is>
       </c>
-      <c r="B11" s="7" t="inlineStr">
+      <c r="C11" s="7" t="inlineStr">
         <is>
           <t>char</t>
         </is>
       </c>
-      <c r="C11" s="7" t="inlineStr"/>
-      <c r="D11" s="7" t="inlineStr">
+      <c r="D11" s="7" t="inlineStr"/>
+      <c r="E11" s="7" t="inlineStr">
         <is>
           <t>phone</t>
         </is>
       </c>
-      <c r="E11" s="7" t="inlineStr">
+      <c r="F11" s="7" t="inlineStr">
         <is>
           <t>Phone</t>
         </is>
       </c>
-      <c r="F11" s="7" t="inlineStr">
+      <c r="G11" s="7" t="inlineStr">
         <is>
           <t>電話</t>
         </is>
       </c>
-      <c r="G11" s="8" t="inlineStr"/>
+      <c r="H11" s="8" t="inlineStr">
+        <is>
+          <t>電話</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
+          <t>聯絡人</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
           <t>res.partner</t>
         </is>
       </c>
-      <c r="B12" s="5" t="inlineStr">
+      <c r="C12" s="5" t="inlineStr">
         <is>
           <t>char</t>
         </is>
       </c>
-      <c r="C12" s="5" t="inlineStr"/>
-      <c r="D12" s="5" t="inlineStr">
+      <c r="D12" s="5" t="inlineStr"/>
+      <c r="E12" s="5" t="inlineStr">
         <is>
           <t>street</t>
         </is>
       </c>
-      <c r="E12" s="5" t="inlineStr">
+      <c r="F12" s="5" t="inlineStr">
         <is>
           <t>Street</t>
         </is>
       </c>
-      <c r="F12" s="5" t="inlineStr">
+      <c r="G12" s="5" t="inlineStr">
         <is>
           <t>街道</t>
         </is>
       </c>
-      <c r="G12" s="6" t="inlineStr"/>
+      <c r="H12" s="6" t="inlineStr">
+        <is>
+          <t>街道</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="7" t="inlineStr">
         <is>
+          <t>聯絡人</t>
+        </is>
+      </c>
+      <c r="B13" s="7" t="inlineStr">
+        <is>
           <t>res.partner</t>
         </is>
       </c>
-      <c r="B13" s="7" t="inlineStr">
+      <c r="C13" s="7" t="inlineStr">
         <is>
           <t>char</t>
         </is>
       </c>
-      <c r="C13" s="7" t="inlineStr"/>
-      <c r="D13" s="7" t="inlineStr">
+      <c r="D13" s="7" t="inlineStr"/>
+      <c r="E13" s="7" t="inlineStr">
         <is>
           <t>zip</t>
         </is>
       </c>
-      <c r="E13" s="7" t="inlineStr">
+      <c r="F13" s="7" t="inlineStr">
         <is>
           <t>Zip</t>
         </is>
       </c>
-      <c r="F13" s="7" t="inlineStr">
+      <c r="G13" s="7" t="inlineStr">
         <is>
           <t>郵遞區號</t>
         </is>
       </c>
-      <c r="G13" s="8" t="inlineStr"/>
+      <c r="H13" s="8" t="inlineStr">
+        <is>
+          <t>郵遞區號</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
+          <t>聯絡人</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
           <t>res.partner</t>
         </is>
       </c>
-      <c r="B14" s="5" t="inlineStr">
+      <c r="C14" s="5" t="inlineStr">
         <is>
           <t>char</t>
         </is>
       </c>
-      <c r="C14" s="5" t="inlineStr"/>
-      <c r="D14" s="5" t="inlineStr">
+      <c r="D14" s="5" t="inlineStr"/>
+      <c r="E14" s="5" t="inlineStr">
         <is>
           <t>city</t>
         </is>
       </c>
-      <c r="E14" s="5" t="inlineStr">
+      <c r="F14" s="5" t="inlineStr">
         <is>
           <t>City</t>
         </is>
       </c>
-      <c r="F14" s="5" t="inlineStr">
+      <c r="G14" s="5" t="inlineStr">
         <is>
           <t>城市</t>
         </is>
       </c>
-      <c r="G14" s="6" t="inlineStr">
-        <is>
-          <t>純文字</t>
+      <c r="H14" s="6" t="inlineStr">
+        <is>
+          <t>城市 · 純文字</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="7" t="inlineStr">
         <is>
+          <t>聯絡人</t>
+        </is>
+      </c>
+      <c r="B15" s="7" t="inlineStr">
+        <is>
           <t>res.partner</t>
         </is>
       </c>
-      <c r="B15" s="7" t="inlineStr">
+      <c r="C15" s="7" t="inlineStr">
         <is>
           <t>many2one</t>
         </is>
       </c>
-      <c r="C15" s="7" t="inlineStr">
+      <c r="D15" s="7" t="inlineStr">
         <is>
           <t>FK</t>
         </is>
       </c>
-      <c r="D15" s="7" t="inlineStr">
+      <c r="E15" s="7" t="inlineStr">
         <is>
           <t>country_id</t>
         </is>
       </c>
-      <c r="E15" s="7" t="inlineStr">
+      <c r="F15" s="7" t="inlineStr">
         <is>
           <t>Country</t>
         </is>
       </c>
-      <c r="F15" s="7" t="inlineStr">
+      <c r="G15" s="7" t="inlineStr">
         <is>
           <t>國家</t>
         </is>
       </c>
-      <c r="G15" s="8" t="inlineStr">
-        <is>
-          <t>選填</t>
+      <c r="H15" s="8" t="inlineStr">
+        <is>
+          <t>國家 · 選填</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
+          <t>聯絡人</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="inlineStr">
+        <is>
           <t>res.partner</t>
         </is>
       </c>
-      <c r="B16" s="5" t="inlineStr">
+      <c r="C16" s="5" t="inlineStr">
         <is>
           <t>many2one</t>
         </is>
       </c>
-      <c r="C16" s="5" t="inlineStr">
+      <c r="D16" s="5" t="inlineStr">
         <is>
           <t>FK</t>
         </is>
       </c>
-      <c r="D16" s="5" t="inlineStr">
+      <c r="E16" s="5" t="inlineStr">
         <is>
           <t>state_id</t>
         </is>
       </c>
-      <c r="E16" s="5" t="inlineStr">
+      <c r="F16" s="5" t="inlineStr">
         <is>
           <t>State</t>
         </is>
       </c>
-      <c r="F16" s="5" t="inlineStr">
+      <c r="G16" s="5" t="inlineStr">
         <is>
           <t>狀態</t>
         </is>
       </c>
-      <c r="G16" s="6" t="inlineStr">
-        <is>
-          <t>選填</t>
+      <c r="H16" s="6" t="inlineStr">
+        <is>
+          <t>狀態 · 選填</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="7" t="inlineStr">
         <is>
+          <t>聯絡人</t>
+        </is>
+      </c>
+      <c r="B17" s="7" t="inlineStr">
+        <is>
           <t>res.partner</t>
         </is>
       </c>
-      <c r="B17" s="7" t="inlineStr">
+      <c r="C17" s="7" t="inlineStr">
         <is>
           <t>many2one</t>
         </is>
       </c>
-      <c r="C17" s="7" t="inlineStr">
+      <c r="D17" s="7" t="inlineStr">
         <is>
           <t>FK</t>
         </is>
       </c>
-      <c r="D17" s="7" t="inlineStr">
+      <c r="E17" s="7" t="inlineStr">
         <is>
           <t>city_id</t>
         </is>
       </c>
-      <c r="E17" s="7" t="inlineStr">
+      <c r="F17" s="7" t="inlineStr">
         <is>
           <t>City ID</t>
         </is>
       </c>
-      <c r="F17" s="7" t="inlineStr">
+      <c r="G17" s="7" t="inlineStr">
         <is>
           <t>城市識別碼</t>
         </is>
       </c>
-      <c r="G17" s="8" t="inlineStr">
-        <is>
-          <t>選填</t>
+      <c r="H17" s="8" t="inlineStr">
+        <is>
+          <t>城市識別碼 · 選填</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
+          <t>聯絡人</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="inlineStr">
+        <is>
           <t>res.partner</t>
         </is>
       </c>
-      <c r="B18" s="5" t="inlineStr">
+      <c r="C18" s="5" t="inlineStr">
         <is>
           <t>many2one</t>
         </is>
       </c>
-      <c r="C18" s="5" t="inlineStr">
+      <c r="D18" s="5" t="inlineStr">
         <is>
           <t>FK</t>
         </is>
       </c>
-      <c r="D18" s="5" t="inlineStr">
+      <c r="E18" s="5" t="inlineStr">
         <is>
           <t>industry_id</t>
         </is>
       </c>
-      <c r="E18" s="5" t="inlineStr">
+      <c r="F18" s="5" t="inlineStr">
         <is>
           <t>Industry</t>
         </is>
       </c>
-      <c r="F18" s="5" t="inlineStr">
+      <c r="G18" s="5" t="inlineStr">
         <is>
           <t>行業</t>
         </is>
       </c>
-      <c r="G18" s="6" t="inlineStr">
-        <is>
-          <t>選填</t>
+      <c r="H18" s="6" t="inlineStr">
+        <is>
+          <t>行業 · 選填</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="7" t="inlineStr">
         <is>
+          <t>聯絡人</t>
+        </is>
+      </c>
+      <c r="B19" s="7" t="inlineStr">
+        <is>
           <t>res.partner</t>
         </is>
       </c>
-      <c r="B19" s="7" t="inlineStr">
+      <c r="C19" s="7" t="inlineStr">
         <is>
           <t>many2one</t>
         </is>
       </c>
-      <c r="C19" s="7" t="inlineStr">
+      <c r="D19" s="7" t="inlineStr">
         <is>
           <t>FK</t>
         </is>
       </c>
-      <c r="D19" s="7" t="inlineStr">
+      <c r="E19" s="7" t="inlineStr">
         <is>
           <t>user_id</t>
         </is>
       </c>
-      <c r="E19" s="7" t="inlineStr">
+      <c r="F19" s="7" t="inlineStr">
         <is>
           <t>Salesperson</t>
         </is>
       </c>
-      <c r="F19" s="7" t="inlineStr">
+      <c r="G19" s="7" t="inlineStr">
         <is>
           <t>銷售員</t>
         </is>
       </c>
-      <c r="G19" s="8" t="inlineStr">
-        <is>
-          <t>compute 可覆寫</t>
+      <c r="H19" s="8" t="inlineStr">
+        <is>
+          <t>銷售員 · compute 可覆寫</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
+          <t>聯絡人</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="inlineStr">
+        <is>
           <t>res.partner</t>
         </is>
       </c>
-      <c r="B20" s="5" t="inlineStr">
+      <c r="C20" s="5" t="inlineStr">
         <is>
           <t>many2one</t>
         </is>
       </c>
-      <c r="C20" s="5" t="inlineStr">
+      <c r="D20" s="5" t="inlineStr">
         <is>
           <t>FK</t>
         </is>
       </c>
-      <c r="D20" s="5" t="inlineStr">
+      <c r="E20" s="5" t="inlineStr">
         <is>
           <t>buyer_id</t>
         </is>
       </c>
-      <c r="E20" s="5" t="inlineStr">
+      <c r="F20" s="5" t="inlineStr">
         <is>
           <t>Buyer</t>
         </is>
       </c>
-      <c r="F20" s="5" t="inlineStr">
+      <c r="G20" s="5" t="inlineStr">
         <is>
           <t>買方</t>
         </is>
       </c>
-      <c r="G20" s="6" t="inlineStr">
-        <is>
-          <t>選填</t>
+      <c r="H20" s="6" t="inlineStr">
+        <is>
+          <t>買方 · 選填</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="7" t="inlineStr">
         <is>
+          <t>聯絡人</t>
+        </is>
+      </c>
+      <c r="B21" s="7" t="inlineStr">
+        <is>
           <t>res.partner</t>
         </is>
       </c>
-      <c r="B21" s="7" t="inlineStr">
+      <c r="C21" s="7" t="inlineStr">
         <is>
           <t>many2one</t>
         </is>
       </c>
-      <c r="C21" s="7" t="inlineStr">
+      <c r="D21" s="7" t="inlineStr">
         <is>
           <t>FK</t>
         </is>
       </c>
-      <c r="D21" s="7" t="inlineStr">
+      <c r="E21" s="7" t="inlineStr">
         <is>
           <t>company_id</t>
         </is>
       </c>
-      <c r="E21" s="7" t="inlineStr">
+      <c r="F21" s="7" t="inlineStr">
         <is>
           <t>Company</t>
         </is>
       </c>
-      <c r="F21" s="7" t="inlineStr">
+      <c r="G21" s="7" t="inlineStr">
         <is>
           <t>公司</t>
         </is>
       </c>
-      <c r="G21" s="8" t="inlineStr">
-        <is>
-          <t>選填</t>
+      <c r="H21" s="8" t="inlineStr">
+        <is>
+          <t>公司 · 選填</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
+          <t>聯絡人</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="inlineStr">
+        <is>
           <t>res.partner</t>
         </is>
       </c>
-      <c r="B22" s="5" t="inlineStr">
+      <c r="C22" s="5" t="inlineStr">
         <is>
           <t>many2one</t>
         </is>
       </c>
-      <c r="C22" s="5" t="inlineStr">
+      <c r="D22" s="5" t="inlineStr">
         <is>
           <t>FK</t>
         </is>
       </c>
-      <c r="D22" s="5" t="inlineStr">
+      <c r="E22" s="5" t="inlineStr">
         <is>
           <t>property_payment_term_id</t>
         </is>
       </c>
-      <c r="E22" s="5" t="inlineStr">
+      <c r="F22" s="5" t="inlineStr">
         <is>
           <t>Customer Payment Terms</t>
         </is>
       </c>
-      <c r="F22" s="5" t="inlineStr">
+      <c r="G22" s="5" t="inlineStr">
         <is>
           <t>客戶支付條款</t>
         </is>
       </c>
-      <c r="G22" s="6" t="inlineStr">
+      <c r="H22" s="6" t="inlineStr">
         <is>
           <t>客戶付款條件</t>
         </is>
@@ -1425,35 +1568,40 @@
     <row r="23">
       <c r="A23" s="7" t="inlineStr">
         <is>
+          <t>聯絡人</t>
+        </is>
+      </c>
+      <c r="B23" s="7" t="inlineStr">
+        <is>
           <t>res.partner</t>
         </is>
       </c>
-      <c r="B23" s="7" t="inlineStr">
+      <c r="C23" s="7" t="inlineStr">
         <is>
           <t>many2one</t>
         </is>
       </c>
-      <c r="C23" s="7" t="inlineStr">
+      <c r="D23" s="7" t="inlineStr">
         <is>
           <t>FK</t>
         </is>
       </c>
-      <c r="D23" s="7" t="inlineStr">
+      <c r="E23" s="7" t="inlineStr">
         <is>
           <t>property_supplier_payment_term_id</t>
         </is>
       </c>
-      <c r="E23" s="7" t="inlineStr">
+      <c r="F23" s="7" t="inlineStr">
         <is>
           <t>Vendor Payment Terms</t>
         </is>
       </c>
-      <c r="F23" s="7" t="inlineStr">
+      <c r="G23" s="7" t="inlineStr">
         <is>
           <t>供應商支付條款</t>
         </is>
       </c>
-      <c r="G23" s="8" t="inlineStr">
+      <c r="H23" s="8" t="inlineStr">
         <is>
           <t>供應商付款條件</t>
         </is>
@@ -1462,35 +1610,40 @@
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
+          <t>聯絡人</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="inlineStr">
+        <is>
           <t>res.partner</t>
         </is>
       </c>
-      <c r="B24" s="5" t="inlineStr">
+      <c r="C24" s="5" t="inlineStr">
         <is>
           <t>many2one</t>
         </is>
       </c>
-      <c r="C24" s="5" t="inlineStr">
+      <c r="D24" s="5" t="inlineStr">
         <is>
           <t>FK</t>
         </is>
       </c>
-      <c r="D24" s="5" t="inlineStr">
+      <c r="E24" s="5" t="inlineStr">
         <is>
           <t>property_account_receivable_id</t>
         </is>
       </c>
-      <c r="E24" s="5" t="inlineStr">
+      <c r="F24" s="5" t="inlineStr">
         <is>
           <t>Account Receivable</t>
         </is>
       </c>
-      <c r="F24" s="5" t="inlineStr">
+      <c r="G24" s="5" t="inlineStr">
         <is>
           <t>應收賬戶</t>
         </is>
       </c>
-      <c r="G24" s="6" t="inlineStr">
+      <c r="H24" s="6" t="inlineStr">
         <is>
           <t>應收科目</t>
         </is>
@@ -1499,35 +1652,40 @@
     <row r="25">
       <c r="A25" s="7" t="inlineStr">
         <is>
+          <t>聯絡人</t>
+        </is>
+      </c>
+      <c r="B25" s="7" t="inlineStr">
+        <is>
           <t>res.partner</t>
         </is>
       </c>
-      <c r="B25" s="7" t="inlineStr">
+      <c r="C25" s="7" t="inlineStr">
         <is>
           <t>many2one</t>
         </is>
       </c>
-      <c r="C25" s="7" t="inlineStr">
+      <c r="D25" s="7" t="inlineStr">
         <is>
           <t>FK</t>
         </is>
       </c>
-      <c r="D25" s="7" t="inlineStr">
+      <c r="E25" s="7" t="inlineStr">
         <is>
           <t>property_account_payable_id</t>
         </is>
       </c>
-      <c r="E25" s="7" t="inlineStr">
+      <c r="F25" s="7" t="inlineStr">
         <is>
           <t>Account Payable</t>
         </is>
       </c>
-      <c r="F25" s="7" t="inlineStr">
+      <c r="G25" s="7" t="inlineStr">
         <is>
           <t>應付賬戶</t>
         </is>
       </c>
-      <c r="G25" s="8" t="inlineStr">
+      <c r="H25" s="8" t="inlineStr">
         <is>
           <t>應付科目</t>
         </is>
@@ -1536,97 +1694,112 @@
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
+          <t>聯絡人</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="inlineStr">
+        <is>
           <t>res.partner</t>
         </is>
       </c>
-      <c r="B26" s="5" t="inlineStr">
+      <c r="C26" s="5" t="inlineStr">
         <is>
           <t>selection</t>
         </is>
       </c>
-      <c r="C26" s="5" t="inlineStr"/>
-      <c r="D26" s="5" t="inlineStr">
+      <c r="D26" s="5" t="inlineStr"/>
+      <c r="E26" s="5" t="inlineStr">
         <is>
           <t>autopost_bills</t>
         </is>
       </c>
-      <c r="E26" s="5" t="inlineStr">
+      <c r="F26" s="5" t="inlineStr">
         <is>
           <t>Auto-post bills</t>
         </is>
       </c>
-      <c r="F26" s="5" t="inlineStr">
+      <c r="G26" s="5" t="inlineStr">
         <is>
           <t>自動過賬賬單</t>
         </is>
       </c>
-      <c r="G26" s="6" t="inlineStr">
-        <is>
-          <t>required 有預設</t>
+      <c r="H26" s="6" t="inlineStr">
+        <is>
+          <t>自動過賬賬單 · required 有預設</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="7" t="inlineStr">
         <is>
+          <t>聯絡人</t>
+        </is>
+      </c>
+      <c r="B27" s="7" t="inlineStr">
+        <is>
           <t>res.partner</t>
         </is>
       </c>
-      <c r="B27" s="7" t="inlineStr">
+      <c r="C27" s="7" t="inlineStr">
         <is>
           <t>selection</t>
         </is>
       </c>
-      <c r="C27" s="7" t="inlineStr"/>
-      <c r="D27" s="7" t="inlineStr">
+      <c r="D27" s="7" t="inlineStr"/>
+      <c r="E27" s="7" t="inlineStr">
         <is>
           <t>group_on</t>
         </is>
       </c>
-      <c r="E27" s="7" t="inlineStr">
+      <c r="F27" s="7" t="inlineStr">
         <is>
           <t>Week Day</t>
         </is>
       </c>
-      <c r="F27" s="7" t="inlineStr">
+      <c r="G27" s="7" t="inlineStr">
         <is>
           <t>平日</t>
         </is>
       </c>
-      <c r="G27" s="8" t="inlineStr">
-        <is>
-          <t>required 有預設</t>
+      <c r="H27" s="8" t="inlineStr">
+        <is>
+          <t>平日 · required 有預設</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
+          <t>聯絡人</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="inlineStr">
+        <is>
           <t>res.partner</t>
         </is>
       </c>
-      <c r="B28" s="5" t="inlineStr">
+      <c r="C28" s="5" t="inlineStr">
         <is>
           <t>selection</t>
         </is>
       </c>
-      <c r="C28" s="5" t="inlineStr"/>
-      <c r="D28" s="5" t="inlineStr">
+      <c r="D28" s="5" t="inlineStr"/>
+      <c r="E28" s="5" t="inlineStr">
         <is>
           <t>group_rfq</t>
         </is>
       </c>
-      <c r="E28" s="5" t="inlineStr">
+      <c r="F28" s="5" t="inlineStr">
         <is>
           <t>Group RFQ</t>
         </is>
       </c>
-      <c r="F28" s="5" t="inlineStr">
+      <c r="G28" s="5" t="inlineStr">
         <is>
           <t>（無官方繁中）</t>
         </is>
       </c>
-      <c r="G28" s="6" t="inlineStr">
+      <c r="H28" s="6" t="inlineStr">
         <is>
           <t>required 有預設</t>
         </is>
@@ -1635,513 +1808,604 @@
     <row r="29">
       <c r="A29" s="7" t="inlineStr">
         <is>
+          <t>聯絡人</t>
+        </is>
+      </c>
+      <c r="B29" s="7" t="inlineStr">
+        <is>
           <t>res.country</t>
         </is>
       </c>
-      <c r="B29" s="7" t="inlineStr">
+      <c r="C29" s="7" t="inlineStr">
         <is>
           <t>integer</t>
         </is>
       </c>
-      <c r="C29" s="7" t="inlineStr">
+      <c r="D29" s="7" t="inlineStr">
         <is>
           <t>PK</t>
         </is>
       </c>
-      <c r="D29" s="7" t="inlineStr">
+      <c r="E29" s="7" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="E29" s="7" t="inlineStr">
+      <c r="F29" s="7" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="F29" s="7" t="inlineStr">
+      <c r="G29" s="7" t="inlineStr">
         <is>
           <t>識別號</t>
         </is>
       </c>
-      <c r="G29" s="8" t="inlineStr"/>
+      <c r="H29" s="8" t="inlineStr">
+        <is>
+          <t>識別號</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
+          <t>聯絡人</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="inlineStr">
+        <is>
           <t>res.country</t>
         </is>
       </c>
-      <c r="B30" s="5" t="inlineStr">
+      <c r="C30" s="5" t="inlineStr">
         <is>
           <t>char</t>
         </is>
       </c>
-      <c r="C30" s="5" t="inlineStr"/>
-      <c r="D30" s="5" t="inlineStr">
+      <c r="D30" s="5" t="inlineStr"/>
+      <c r="E30" s="5" t="inlineStr">
         <is>
           <t>code</t>
         </is>
       </c>
-      <c r="E30" s="5" t="inlineStr">
+      <c r="F30" s="5" t="inlineStr">
         <is>
           <t>Country Code</t>
         </is>
       </c>
-      <c r="F30" s="5" t="inlineStr">
+      <c r="G30" s="5" t="inlineStr">
         <is>
           <t>國家/地區代碼</t>
         </is>
       </c>
-      <c r="G30" s="6" t="inlineStr">
-        <is>
-          <t>required</t>
+      <c r="H30" s="6" t="inlineStr">
+        <is>
+          <t>國家/地區代碼 · required</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="7" t="inlineStr">
         <is>
+          <t>聯絡人</t>
+        </is>
+      </c>
+      <c r="B31" s="7" t="inlineStr">
+        <is>
           <t>res.country</t>
         </is>
       </c>
-      <c r="B31" s="7" t="inlineStr">
+      <c r="C31" s="7" t="inlineStr">
         <is>
           <t>char</t>
         </is>
       </c>
-      <c r="C31" s="7" t="inlineStr"/>
-      <c r="D31" s="7" t="inlineStr">
+      <c r="D31" s="7" t="inlineStr"/>
+      <c r="E31" s="7" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="E31" s="7" t="inlineStr">
+      <c r="F31" s="7" t="inlineStr">
         <is>
           <t>Country Name</t>
         </is>
       </c>
-      <c r="F31" s="7" t="inlineStr">
+      <c r="G31" s="7" t="inlineStr">
         <is>
           <t>國家名稱</t>
         </is>
       </c>
-      <c r="G31" s="8" t="inlineStr">
-        <is>
-          <t>required</t>
+      <c r="H31" s="8" t="inlineStr">
+        <is>
+          <t>國家名稱 · required</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
         <is>
+          <t>聯絡人</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="inlineStr">
+        <is>
           <t>res.country.state</t>
         </is>
       </c>
-      <c r="B32" s="5" t="inlineStr">
+      <c r="C32" s="5" t="inlineStr">
         <is>
           <t>integer</t>
         </is>
       </c>
-      <c r="C32" s="5" t="inlineStr">
+      <c r="D32" s="5" t="inlineStr">
         <is>
           <t>PK</t>
         </is>
       </c>
-      <c r="D32" s="5" t="inlineStr">
+      <c r="E32" s="5" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="E32" s="5" t="inlineStr">
+      <c r="F32" s="5" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="F32" s="5" t="inlineStr">
+      <c r="G32" s="5" t="inlineStr">
         <is>
           <t>識別號</t>
         </is>
       </c>
-      <c r="G32" s="6" t="inlineStr"/>
+      <c r="H32" s="6" t="inlineStr">
+        <is>
+          <t>識別號</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="7" t="inlineStr">
         <is>
+          <t>聯絡人</t>
+        </is>
+      </c>
+      <c r="B33" s="7" t="inlineStr">
+        <is>
           <t>res.country.state</t>
         </is>
       </c>
-      <c r="B33" s="7" t="inlineStr">
+      <c r="C33" s="7" t="inlineStr">
         <is>
           <t>char</t>
         </is>
       </c>
-      <c r="C33" s="7" t="inlineStr"/>
-      <c r="D33" s="7" t="inlineStr">
+      <c r="D33" s="7" t="inlineStr"/>
+      <c r="E33" s="7" t="inlineStr">
         <is>
           <t>code</t>
         </is>
       </c>
-      <c r="E33" s="7" t="inlineStr">
+      <c r="F33" s="7" t="inlineStr">
         <is>
           <t>State Code</t>
         </is>
       </c>
-      <c r="F33" s="7" t="inlineStr">
+      <c r="G33" s="7" t="inlineStr">
         <is>
           <t>州/省代碼</t>
         </is>
       </c>
-      <c r="G33" s="8" t="inlineStr">
-        <is>
-          <t>required</t>
+      <c r="H33" s="8" t="inlineStr">
+        <is>
+          <t>州/省代碼 · required</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
         <is>
+          <t>聯絡人</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="inlineStr">
+        <is>
           <t>res.country.state</t>
         </is>
       </c>
-      <c r="B34" s="5" t="inlineStr">
+      <c r="C34" s="5" t="inlineStr">
         <is>
           <t>char</t>
         </is>
       </c>
-      <c r="C34" s="5" t="inlineStr"/>
-      <c r="D34" s="5" t="inlineStr">
+      <c r="D34" s="5" t="inlineStr"/>
+      <c r="E34" s="5" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="E34" s="5" t="inlineStr">
+      <c r="F34" s="5" t="inlineStr">
         <is>
           <t>State Name</t>
         </is>
       </c>
-      <c r="F34" s="5" t="inlineStr">
+      <c r="G34" s="5" t="inlineStr">
         <is>
           <t>州/省名稱</t>
         </is>
       </c>
-      <c r="G34" s="6" t="inlineStr">
-        <is>
-          <t>required</t>
+      <c r="H34" s="6" t="inlineStr">
+        <is>
+          <t>州/省名稱 · required</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="7" t="inlineStr">
         <is>
+          <t>聯絡人</t>
+        </is>
+      </c>
+      <c r="B35" s="7" t="inlineStr">
+        <is>
           <t>res.country.state</t>
         </is>
       </c>
-      <c r="B35" s="7" t="inlineStr">
+      <c r="C35" s="7" t="inlineStr">
         <is>
           <t>many2one</t>
         </is>
       </c>
-      <c r="C35" s="7" t="inlineStr">
+      <c r="D35" s="7" t="inlineStr">
         <is>
           <t>FK</t>
         </is>
       </c>
-      <c r="D35" s="7" t="inlineStr">
+      <c r="E35" s="7" t="inlineStr">
         <is>
           <t>country_id</t>
         </is>
       </c>
-      <c r="E35" s="7" t="inlineStr">
+      <c r="F35" s="7" t="inlineStr">
         <is>
           <t>Country</t>
         </is>
       </c>
-      <c r="F35" s="7" t="inlineStr">
+      <c r="G35" s="7" t="inlineStr">
         <is>
           <t>國家 / 地區</t>
         </is>
       </c>
-      <c r="G35" s="8" t="inlineStr">
-        <is>
-          <t>required</t>
+      <c r="H35" s="8" t="inlineStr">
+        <is>
+          <t>國家 / 地區 · required</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="5" t="inlineStr">
         <is>
+          <t>聯絡人</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="inlineStr">
+        <is>
           <t>res.city</t>
         </is>
       </c>
-      <c r="B36" s="5" t="inlineStr">
+      <c r="C36" s="5" t="inlineStr">
         <is>
           <t>integer</t>
         </is>
       </c>
-      <c r="C36" s="5" t="inlineStr">
+      <c r="D36" s="5" t="inlineStr">
         <is>
           <t>PK</t>
         </is>
       </c>
-      <c r="D36" s="5" t="inlineStr">
+      <c r="E36" s="5" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="E36" s="5" t="inlineStr">
+      <c r="F36" s="5" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="F36" s="5" t="inlineStr">
+      <c r="G36" s="5" t="inlineStr">
         <is>
           <t>識別號</t>
         </is>
       </c>
-      <c r="G36" s="6" t="inlineStr"/>
+      <c r="H36" s="6" t="inlineStr">
+        <is>
+          <t>識別號</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="7" t="inlineStr">
         <is>
+          <t>聯絡人</t>
+        </is>
+      </c>
+      <c r="B37" s="7" t="inlineStr">
+        <is>
           <t>res.city</t>
         </is>
       </c>
-      <c r="B37" s="7" t="inlineStr">
+      <c r="C37" s="7" t="inlineStr">
         <is>
           <t>char</t>
         </is>
       </c>
-      <c r="C37" s="7" t="inlineStr"/>
-      <c r="D37" s="7" t="inlineStr">
+      <c r="D37" s="7" t="inlineStr"/>
+      <c r="E37" s="7" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="E37" s="7" t="inlineStr">
+      <c r="F37" s="7" t="inlineStr">
         <is>
           <t>Name</t>
         </is>
       </c>
-      <c r="F37" s="7" t="inlineStr">
+      <c r="G37" s="7" t="inlineStr">
         <is>
           <t>名稱</t>
         </is>
       </c>
-      <c r="G37" s="8" t="inlineStr">
-        <is>
-          <t>required</t>
+      <c r="H37" s="8" t="inlineStr">
+        <is>
+          <t>名稱 · required</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="5" t="inlineStr">
         <is>
+          <t>聯絡人</t>
+        </is>
+      </c>
+      <c r="B38" s="5" t="inlineStr">
+        <is>
           <t>res.city</t>
         </is>
       </c>
-      <c r="B38" s="5" t="inlineStr">
+      <c r="C38" s="5" t="inlineStr">
         <is>
           <t>many2one</t>
         </is>
       </c>
-      <c r="C38" s="5" t="inlineStr">
+      <c r="D38" s="5" t="inlineStr">
         <is>
           <t>FK</t>
         </is>
       </c>
-      <c r="D38" s="5" t="inlineStr">
+      <c r="E38" s="5" t="inlineStr">
         <is>
           <t>country_id</t>
         </is>
       </c>
-      <c r="E38" s="5" t="inlineStr">
+      <c r="F38" s="5" t="inlineStr">
         <is>
           <t>Country</t>
         </is>
       </c>
-      <c r="F38" s="5" t="inlineStr">
+      <c r="G38" s="5" t="inlineStr">
         <is>
           <t>國家</t>
         </is>
       </c>
-      <c r="G38" s="6" t="inlineStr">
-        <is>
-          <t>required</t>
+      <c r="H38" s="6" t="inlineStr">
+        <is>
+          <t>國家 · required</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="7" t="inlineStr">
         <is>
+          <t>聯絡人</t>
+        </is>
+      </c>
+      <c r="B39" s="7" t="inlineStr">
+        <is>
           <t>res.city</t>
         </is>
       </c>
-      <c r="B39" s="7" t="inlineStr">
+      <c r="C39" s="7" t="inlineStr">
         <is>
           <t>many2one</t>
         </is>
       </c>
-      <c r="C39" s="7" t="inlineStr">
+      <c r="D39" s="7" t="inlineStr">
         <is>
           <t>FK</t>
         </is>
       </c>
-      <c r="D39" s="7" t="inlineStr">
+      <c r="E39" s="7" t="inlineStr">
         <is>
           <t>state_id</t>
         </is>
       </c>
-      <c r="E39" s="7" t="inlineStr">
+      <c r="F39" s="7" t="inlineStr">
         <is>
           <t>State</t>
         </is>
       </c>
-      <c r="F39" s="7" t="inlineStr">
+      <c r="G39" s="7" t="inlineStr">
         <is>
           <t>州/省</t>
         </is>
       </c>
-      <c r="G39" s="8" t="inlineStr">
-        <is>
-          <t>選填</t>
+      <c r="H39" s="8" t="inlineStr">
+        <is>
+          <t>州/省 · 選填</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="5" t="inlineStr">
         <is>
+          <t>聯絡人</t>
+        </is>
+      </c>
+      <c r="B40" s="5" t="inlineStr">
+        <is>
           <t>res.partner.category</t>
         </is>
       </c>
-      <c r="B40" s="5" t="inlineStr">
+      <c r="C40" s="5" t="inlineStr">
         <is>
           <t>integer</t>
         </is>
       </c>
-      <c r="C40" s="5" t="inlineStr">
+      <c r="D40" s="5" t="inlineStr">
         <is>
           <t>PK</t>
         </is>
       </c>
-      <c r="D40" s="5" t="inlineStr">
+      <c r="E40" s="5" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="E40" s="5" t="inlineStr">
+      <c r="F40" s="5" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="F40" s="5" t="inlineStr">
+      <c r="G40" s="5" t="inlineStr">
         <is>
           <t>識別號</t>
         </is>
       </c>
-      <c r="G40" s="6" t="inlineStr"/>
+      <c r="H40" s="6" t="inlineStr">
+        <is>
+          <t>識別號</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="7" t="inlineStr">
         <is>
+          <t>聯絡人</t>
+        </is>
+      </c>
+      <c r="B41" s="7" t="inlineStr">
+        <is>
           <t>res.partner.category</t>
         </is>
       </c>
-      <c r="B41" s="7" t="inlineStr">
+      <c r="C41" s="7" t="inlineStr">
         <is>
           <t>char</t>
         </is>
       </c>
-      <c r="C41" s="7" t="inlineStr"/>
-      <c r="D41" s="7" t="inlineStr">
+      <c r="D41" s="7" t="inlineStr"/>
+      <c r="E41" s="7" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="E41" s="7" t="inlineStr">
+      <c r="F41" s="7" t="inlineStr">
         <is>
           <t>Name</t>
         </is>
       </c>
-      <c r="F41" s="7" t="inlineStr">
+      <c r="G41" s="7" t="inlineStr">
         <is>
           <t>名稱</t>
         </is>
       </c>
-      <c r="G41" s="8" t="inlineStr">
-        <is>
-          <t>required</t>
+      <c r="H41" s="8" t="inlineStr">
+        <is>
+          <t>名稱 · required</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="5" t="inlineStr">
         <is>
+          <t>聯絡人</t>
+        </is>
+      </c>
+      <c r="B42" s="5" t="inlineStr">
+        <is>
           <t>res.partner.category</t>
         </is>
       </c>
-      <c r="B42" s="5" t="inlineStr">
+      <c r="C42" s="5" t="inlineStr">
         <is>
           <t>many2one</t>
         </is>
       </c>
-      <c r="C42" s="5" t="inlineStr">
+      <c r="D42" s="5" t="inlineStr">
         <is>
           <t>FK</t>
         </is>
       </c>
-      <c r="D42" s="5" t="inlineStr">
+      <c r="E42" s="5" t="inlineStr">
         <is>
           <t>parent_id</t>
         </is>
       </c>
-      <c r="E42" s="5" t="inlineStr">
+      <c r="F42" s="5" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="F42" s="5" t="inlineStr">
+      <c r="G42" s="5" t="inlineStr">
         <is>
           <t>類別</t>
         </is>
       </c>
-      <c r="G42" s="6" t="inlineStr">
-        <is>
-          <t>自身 標籤有階層</t>
+      <c r="H42" s="6" t="inlineStr">
+        <is>
+          <t>類別 · 自身 標籤有階層</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="7" t="inlineStr">
         <is>
+          <t>聯絡人</t>
+        </is>
+      </c>
+      <c r="B43" s="7" t="inlineStr">
+        <is>
           <t>res_partner_res_partner_category_rel</t>
         </is>
       </c>
-      <c r="B43" s="7" t="inlineStr">
+      <c r="C43" s="7" t="inlineStr">
         <is>
           <t>integer</t>
         </is>
       </c>
-      <c r="C43" s="7" t="inlineStr">
+      <c r="D43" s="7" t="inlineStr">
         <is>
           <t>PK,FK</t>
         </is>
       </c>
-      <c r="D43" s="7" t="inlineStr">
+      <c r="E43" s="7" t="inlineStr">
         <is>
           <t>partner_id</t>
         </is>
       </c>
-      <c r="E43" s="7" t="inlineStr">
+      <c r="F43" s="7" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F43" s="7" t="inlineStr">
+      <c r="G43" s="7" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G43" s="8" t="inlineStr">
+      <c r="H43" s="8" t="inlineStr">
         <is>
           <t>中介表欄位，無 model 層標籤；NOT NULL</t>
         </is>
@@ -2150,35 +2414,40 @@
     <row r="44">
       <c r="A44" s="5" t="inlineStr">
         <is>
+          <t>聯絡人</t>
+        </is>
+      </c>
+      <c r="B44" s="5" t="inlineStr">
+        <is>
           <t>res_partner_res_partner_category_rel</t>
         </is>
       </c>
-      <c r="B44" s="5" t="inlineStr">
+      <c r="C44" s="5" t="inlineStr">
         <is>
           <t>integer</t>
         </is>
       </c>
-      <c r="C44" s="5" t="inlineStr">
+      <c r="D44" s="5" t="inlineStr">
         <is>
           <t>PK,FK</t>
         </is>
       </c>
-      <c r="D44" s="5" t="inlineStr">
+      <c r="E44" s="5" t="inlineStr">
         <is>
           <t>category_id</t>
         </is>
       </c>
-      <c r="E44" s="5" t="inlineStr">
+      <c r="F44" s="5" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F44" s="5" t="inlineStr">
+      <c r="G44" s="5" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G44" s="6" t="inlineStr">
+      <c r="H44" s="6" t="inlineStr">
         <is>
           <t>中介表欄位，無 model 層標籤；NOT NULL</t>
         </is>
@@ -2187,340 +2456,406 @@
     <row r="45">
       <c r="A45" s="7" t="inlineStr">
         <is>
+          <t>聯絡人</t>
+        </is>
+      </c>
+      <c r="B45" s="7" t="inlineStr">
+        <is>
           <t>res.partner.industry</t>
         </is>
       </c>
-      <c r="B45" s="7" t="inlineStr">
+      <c r="C45" s="7" t="inlineStr">
         <is>
           <t>integer</t>
         </is>
       </c>
-      <c r="C45" s="7" t="inlineStr">
+      <c r="D45" s="7" t="inlineStr">
         <is>
           <t>PK</t>
         </is>
       </c>
-      <c r="D45" s="7" t="inlineStr">
+      <c r="E45" s="7" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="E45" s="7" t="inlineStr">
+      <c r="F45" s="7" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="F45" s="7" t="inlineStr">
+      <c r="G45" s="7" t="inlineStr">
         <is>
           <t>識別號</t>
         </is>
       </c>
-      <c r="G45" s="8" t="inlineStr"/>
+      <c r="H45" s="8" t="inlineStr">
+        <is>
+          <t>識別號</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="5" t="inlineStr">
         <is>
+          <t>聯絡人</t>
+        </is>
+      </c>
+      <c r="B46" s="5" t="inlineStr">
+        <is>
           <t>res.partner.industry</t>
         </is>
       </c>
-      <c r="B46" s="5" t="inlineStr">
+      <c r="C46" s="5" t="inlineStr">
         <is>
           <t>char</t>
         </is>
       </c>
-      <c r="C46" s="5" t="inlineStr"/>
-      <c r="D46" s="5" t="inlineStr">
+      <c r="D46" s="5" t="inlineStr"/>
+      <c r="E46" s="5" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="E46" s="5" t="inlineStr">
+      <c r="F46" s="5" t="inlineStr">
         <is>
           <t>Name</t>
         </is>
       </c>
-      <c r="F46" s="5" t="inlineStr">
+      <c r="G46" s="5" t="inlineStr">
         <is>
           <t>名稱</t>
         </is>
       </c>
-      <c r="G46" s="6" t="inlineStr">
-        <is>
-          <t>非必填</t>
+      <c r="H46" s="6" t="inlineStr">
+        <is>
+          <t>名稱 · 非必填</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="7" t="inlineStr">
         <is>
+          <t>聯絡人</t>
+        </is>
+      </c>
+      <c r="B47" s="7" t="inlineStr">
+        <is>
           <t>res.users</t>
         </is>
       </c>
-      <c r="B47" s="7" t="inlineStr">
+      <c r="C47" s="7" t="inlineStr">
         <is>
           <t>integer</t>
         </is>
       </c>
-      <c r="C47" s="7" t="inlineStr">
+      <c r="D47" s="7" t="inlineStr">
         <is>
           <t>PK</t>
         </is>
       </c>
-      <c r="D47" s="7" t="inlineStr">
+      <c r="E47" s="7" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="E47" s="7" t="inlineStr">
+      <c r="F47" s="7" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="F47" s="7" t="inlineStr">
+      <c r="G47" s="7" t="inlineStr">
         <is>
           <t>識別號</t>
         </is>
       </c>
-      <c r="G47" s="8" t="inlineStr"/>
+      <c r="H47" s="8" t="inlineStr">
+        <is>
+          <t>識別號</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="5" t="inlineStr">
         <is>
+          <t>聯絡人</t>
+        </is>
+      </c>
+      <c r="B48" s="5" t="inlineStr">
+        <is>
           <t>res.users</t>
         </is>
       </c>
-      <c r="B48" s="5" t="inlineStr">
+      <c r="C48" s="5" t="inlineStr">
         <is>
           <t>many2one</t>
         </is>
       </c>
-      <c r="C48" s="5" t="inlineStr">
+      <c r="D48" s="5" t="inlineStr">
         <is>
           <t>FK</t>
         </is>
       </c>
-      <c r="D48" s="5" t="inlineStr">
+      <c r="E48" s="5" t="inlineStr">
         <is>
           <t>partner_id</t>
         </is>
       </c>
-      <c r="E48" s="5" t="inlineStr">
+      <c r="F48" s="5" t="inlineStr">
         <is>
           <t>Related Partner</t>
         </is>
       </c>
-      <c r="F48" s="5" t="inlineStr">
+      <c r="G48" s="5" t="inlineStr">
         <is>
           <t>相關的合作夥伴</t>
         </is>
       </c>
-      <c r="G48" s="6" t="inlineStr">
-        <is>
-          <t>required</t>
+      <c r="H48" s="6" t="inlineStr">
+        <is>
+          <t>相關的合作夥伴 · required</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="7" t="inlineStr">
         <is>
+          <t>聯絡人</t>
+        </is>
+      </c>
+      <c r="B49" s="7" t="inlineStr">
+        <is>
           <t>res.company</t>
         </is>
       </c>
-      <c r="B49" s="7" t="inlineStr">
+      <c r="C49" s="7" t="inlineStr">
         <is>
           <t>integer</t>
         </is>
       </c>
-      <c r="C49" s="7" t="inlineStr">
+      <c r="D49" s="7" t="inlineStr">
         <is>
           <t>PK</t>
         </is>
       </c>
-      <c r="D49" s="7" t="inlineStr">
+      <c r="E49" s="7" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="E49" s="7" t="inlineStr">
+      <c r="F49" s="7" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="F49" s="7" t="inlineStr">
+      <c r="G49" s="7" t="inlineStr">
         <is>
           <t>識別號</t>
         </is>
       </c>
-      <c r="G49" s="8" t="inlineStr"/>
+      <c r="H49" s="8" t="inlineStr">
+        <is>
+          <t>識別號</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="5" t="inlineStr">
         <is>
+          <t>聯絡人</t>
+        </is>
+      </c>
+      <c r="B50" s="5" t="inlineStr">
+        <is>
           <t>res.company</t>
         </is>
       </c>
-      <c r="B50" s="5" t="inlineStr">
+      <c r="C50" s="5" t="inlineStr">
         <is>
           <t>many2one</t>
         </is>
       </c>
-      <c r="C50" s="5" t="inlineStr">
+      <c r="D50" s="5" t="inlineStr">
         <is>
           <t>FK</t>
         </is>
       </c>
-      <c r="D50" s="5" t="inlineStr">
+      <c r="E50" s="5" t="inlineStr">
         <is>
           <t>partner_id</t>
         </is>
       </c>
-      <c r="E50" s="5" t="inlineStr">
+      <c r="F50" s="5" t="inlineStr">
         <is>
           <t>Partner</t>
         </is>
       </c>
-      <c r="F50" s="5" t="inlineStr">
+      <c r="G50" s="5" t="inlineStr">
         <is>
           <t>業務夥伴</t>
         </is>
       </c>
-      <c r="G50" s="6" t="inlineStr">
-        <is>
-          <t>required</t>
+      <c r="H50" s="6" t="inlineStr">
+        <is>
+          <t>業務夥伴 · required</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="7" t="inlineStr">
         <is>
+          <t>聯絡人</t>
+        </is>
+      </c>
+      <c r="B51" s="7" t="inlineStr">
+        <is>
           <t>res.partner.bank</t>
         </is>
       </c>
-      <c r="B51" s="7" t="inlineStr">
+      <c r="C51" s="7" t="inlineStr">
         <is>
           <t>integer</t>
         </is>
       </c>
-      <c r="C51" s="7" t="inlineStr">
+      <c r="D51" s="7" t="inlineStr">
         <is>
           <t>PK</t>
         </is>
       </c>
-      <c r="D51" s="7" t="inlineStr">
+      <c r="E51" s="7" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="E51" s="7" t="inlineStr">
+      <c r="F51" s="7" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="F51" s="7" t="inlineStr">
+      <c r="G51" s="7" t="inlineStr">
         <is>
           <t>識別號</t>
         </is>
       </c>
-      <c r="G51" s="8" t="inlineStr"/>
+      <c r="H51" s="8" t="inlineStr">
+        <is>
+          <t>識別號</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="5" t="inlineStr">
         <is>
+          <t>聯絡人</t>
+        </is>
+      </c>
+      <c r="B52" s="5" t="inlineStr">
+        <is>
           <t>res.partner.bank</t>
         </is>
       </c>
-      <c r="B52" s="5" t="inlineStr">
+      <c r="C52" s="5" t="inlineStr">
         <is>
           <t>char</t>
         </is>
       </c>
-      <c r="C52" s="5" t="inlineStr"/>
-      <c r="D52" s="5" t="inlineStr">
+      <c r="D52" s="5" t="inlineStr"/>
+      <c r="E52" s="5" t="inlineStr">
         <is>
           <t>acc_number</t>
         </is>
       </c>
-      <c r="E52" s="5" t="inlineStr">
+      <c r="F52" s="5" t="inlineStr">
         <is>
           <t>Account Number</t>
         </is>
       </c>
-      <c r="F52" s="5" t="inlineStr">
+      <c r="G52" s="5" t="inlineStr">
         <is>
           <t>帳戶號碼</t>
         </is>
       </c>
-      <c r="G52" s="6" t="inlineStr">
-        <is>
-          <t>required</t>
+      <c r="H52" s="6" t="inlineStr">
+        <is>
+          <t>帳戶號碼 · required</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="7" t="inlineStr">
         <is>
+          <t>聯絡人</t>
+        </is>
+      </c>
+      <c r="B53" s="7" t="inlineStr">
+        <is>
           <t>res.partner.bank</t>
         </is>
       </c>
-      <c r="B53" s="7" t="inlineStr">
+      <c r="C53" s="7" t="inlineStr">
         <is>
           <t>many2one</t>
         </is>
       </c>
-      <c r="C53" s="7" t="inlineStr">
+      <c r="D53" s="7" t="inlineStr">
         <is>
           <t>FK</t>
         </is>
       </c>
-      <c r="D53" s="7" t="inlineStr">
+      <c r="E53" s="7" t="inlineStr">
         <is>
           <t>partner_id</t>
         </is>
       </c>
-      <c r="E53" s="7" t="inlineStr">
+      <c r="F53" s="7" t="inlineStr">
         <is>
           <t>Account Holder</t>
         </is>
       </c>
-      <c r="F53" s="7" t="inlineStr">
+      <c r="G53" s="7" t="inlineStr">
         <is>
           <t>科目持有人</t>
         </is>
       </c>
-      <c r="G53" s="8" t="inlineStr">
-        <is>
-          <t>required</t>
+      <c r="H53" s="8" t="inlineStr">
+        <is>
+          <t>科目持有人 · required</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="5" t="inlineStr">
         <is>
+          <t>聯絡人</t>
+        </is>
+      </c>
+      <c r="B54" s="5" t="inlineStr">
+        <is>
           <t>res.partner.bank</t>
         </is>
       </c>
-      <c r="B54" s="5" t="inlineStr">
+      <c r="C54" s="5" t="inlineStr">
         <is>
           <t>selection</t>
         </is>
       </c>
-      <c r="C54" s="5" t="inlineStr"/>
-      <c r="D54" s="5" t="inlineStr">
+      <c r="D54" s="5" t="inlineStr"/>
+      <c r="E54" s="5" t="inlineStr">
         <is>
           <t>l10n_us_bank_account_type</t>
         </is>
       </c>
-      <c r="E54" s="5" t="inlineStr">
+      <c r="F54" s="5" t="inlineStr">
         <is>
           <t>Bank Account Type</t>
         </is>
       </c>
-      <c r="F54" s="5" t="inlineStr">
+      <c r="G54" s="5" t="inlineStr">
         <is>
           <t>（無官方繁中）</t>
         </is>
       </c>
-      <c r="G54" s="6" t="inlineStr">
+      <c r="H54" s="6" t="inlineStr">
         <is>
           <t>required 預設 checking</t>
         </is>
@@ -2529,814 +2864,958 @@
     <row r="55">
       <c r="A55" s="7" t="inlineStr">
         <is>
+          <t>聯絡人</t>
+        </is>
+      </c>
+      <c r="B55" s="7" t="inlineStr">
+        <is>
           <t>account.payment.term</t>
         </is>
       </c>
-      <c r="B55" s="7" t="inlineStr">
+      <c r="C55" s="7" t="inlineStr">
         <is>
           <t>integer</t>
         </is>
       </c>
-      <c r="C55" s="7" t="inlineStr">
+      <c r="D55" s="7" t="inlineStr">
         <is>
           <t>PK</t>
         </is>
       </c>
-      <c r="D55" s="7" t="inlineStr">
+      <c r="E55" s="7" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="E55" s="7" t="inlineStr">
+      <c r="F55" s="7" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="F55" s="7" t="inlineStr">
+      <c r="G55" s="7" t="inlineStr">
         <is>
           <t>識別號</t>
         </is>
       </c>
-      <c r="G55" s="8" t="inlineStr"/>
+      <c r="H55" s="8" t="inlineStr">
+        <is>
+          <t>識別號</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="5" t="inlineStr">
         <is>
+          <t>聯絡人</t>
+        </is>
+      </c>
+      <c r="B56" s="5" t="inlineStr">
+        <is>
           <t>account.payment.term</t>
         </is>
       </c>
-      <c r="B56" s="5" t="inlineStr">
+      <c r="C56" s="5" t="inlineStr">
         <is>
           <t>char</t>
         </is>
       </c>
-      <c r="C56" s="5" t="inlineStr"/>
-      <c r="D56" s="5" t="inlineStr">
+      <c r="D56" s="5" t="inlineStr"/>
+      <c r="E56" s="5" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="E56" s="5" t="inlineStr">
+      <c r="F56" s="5" t="inlineStr">
         <is>
           <t>Payment Terms</t>
         </is>
       </c>
-      <c r="F56" s="5" t="inlineStr">
+      <c r="G56" s="5" t="inlineStr">
         <is>
           <t>付款條件</t>
         </is>
       </c>
-      <c r="G56" s="6" t="inlineStr">
-        <is>
-          <t>required</t>
+      <c r="H56" s="6" t="inlineStr">
+        <is>
+          <t>付款條件 · required</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="7" t="inlineStr">
         <is>
+          <t>聯絡人</t>
+        </is>
+      </c>
+      <c r="B57" s="7" t="inlineStr">
+        <is>
           <t>account.payment.term</t>
         </is>
       </c>
-      <c r="B57" s="7" t="inlineStr">
+      <c r="C57" s="7" t="inlineStr">
         <is>
           <t>integer</t>
         </is>
       </c>
-      <c r="C57" s="7" t="inlineStr"/>
-      <c r="D57" s="7" t="inlineStr">
+      <c r="D57" s="7" t="inlineStr"/>
+      <c r="E57" s="7" t="inlineStr">
         <is>
           <t>sequence</t>
         </is>
       </c>
-      <c r="E57" s="7" t="inlineStr">
+      <c r="F57" s="7" t="inlineStr">
         <is>
           <t>Sequence</t>
         </is>
       </c>
-      <c r="F57" s="7" t="inlineStr">
+      <c r="G57" s="7" t="inlineStr">
         <is>
           <t>序列號</t>
         </is>
       </c>
-      <c r="G57" s="8" t="inlineStr">
-        <is>
-          <t>required</t>
+      <c r="H57" s="8" t="inlineStr">
+        <is>
+          <t>序列號 · required</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="5" t="inlineStr">
         <is>
+          <t>聯絡人</t>
+        </is>
+      </c>
+      <c r="B58" s="5" t="inlineStr">
+        <is>
           <t>account.account</t>
         </is>
       </c>
-      <c r="B58" s="5" t="inlineStr">
+      <c r="C58" s="5" t="inlineStr">
         <is>
           <t>integer</t>
         </is>
       </c>
-      <c r="C58" s="5" t="inlineStr">
+      <c r="D58" s="5" t="inlineStr">
         <is>
           <t>PK</t>
         </is>
       </c>
-      <c r="D58" s="5" t="inlineStr">
+      <c r="E58" s="5" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="E58" s="5" t="inlineStr">
+      <c r="F58" s="5" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="F58" s="5" t="inlineStr">
+      <c r="G58" s="5" t="inlineStr">
         <is>
           <t>識別號</t>
         </is>
       </c>
-      <c r="G58" s="6" t="inlineStr"/>
+      <c r="H58" s="6" t="inlineStr">
+        <is>
+          <t>識別號</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="7" t="inlineStr">
         <is>
+          <t>聯絡人</t>
+        </is>
+      </c>
+      <c r="B59" s="7" t="inlineStr">
+        <is>
           <t>account.account</t>
         </is>
       </c>
-      <c r="B59" s="7" t="inlineStr">
+      <c r="C59" s="7" t="inlineStr">
         <is>
           <t>char</t>
         </is>
       </c>
-      <c r="C59" s="7" t="inlineStr"/>
-      <c r="D59" s="7" t="inlineStr">
+      <c r="D59" s="7" t="inlineStr"/>
+      <c r="E59" s="7" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="E59" s="7" t="inlineStr">
+      <c r="F59" s="7" t="inlineStr">
         <is>
           <t>Account Name</t>
         </is>
       </c>
-      <c r="F59" s="7" t="inlineStr">
+      <c r="G59" s="7" t="inlineStr">
         <is>
           <t>帳戶名稱</t>
         </is>
       </c>
-      <c r="G59" s="8" t="inlineStr">
-        <is>
-          <t>required</t>
+      <c r="H59" s="8" t="inlineStr">
+        <is>
+          <t>帳戶名稱 · required</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="5" t="inlineStr">
         <is>
+          <t>聯絡人</t>
+        </is>
+      </c>
+      <c r="B60" s="5" t="inlineStr">
+        <is>
           <t>account.account</t>
         </is>
       </c>
-      <c r="B60" s="5" t="inlineStr">
+      <c r="C60" s="5" t="inlineStr">
         <is>
           <t>selection</t>
         </is>
       </c>
-      <c r="C60" s="5" t="inlineStr"/>
-      <c r="D60" s="5" t="inlineStr">
+      <c r="D60" s="5" t="inlineStr"/>
+      <c r="E60" s="5" t="inlineStr">
         <is>
           <t>account_type</t>
         </is>
       </c>
-      <c r="E60" s="5" t="inlineStr">
+      <c r="F60" s="5" t="inlineStr">
         <is>
           <t>Type</t>
         </is>
       </c>
-      <c r="F60" s="5" t="inlineStr">
+      <c r="G60" s="5" t="inlineStr">
         <is>
           <t>類型</t>
         </is>
       </c>
-      <c r="G60" s="6" t="inlineStr">
-        <is>
-          <t>required</t>
+      <c r="H60" s="6" t="inlineStr">
+        <is>
+          <t>類型 · required</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="7" t="inlineStr">
         <is>
+          <t>商品主檔</t>
+        </is>
+      </c>
+      <c r="B61" s="7" t="inlineStr">
+        <is>
           <t>product.template</t>
         </is>
       </c>
-      <c r="B61" s="7" t="inlineStr">
+      <c r="C61" s="7" t="inlineStr">
         <is>
           <t>integer</t>
         </is>
       </c>
-      <c r="C61" s="7" t="inlineStr">
+      <c r="D61" s="7" t="inlineStr">
         <is>
           <t>PK</t>
         </is>
       </c>
-      <c r="D61" s="7" t="inlineStr">
+      <c r="E61" s="7" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="E61" s="7" t="inlineStr">
+      <c r="F61" s="7" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="F61" s="7" t="inlineStr">
+      <c r="G61" s="7" t="inlineStr">
         <is>
           <t>識別號</t>
         </is>
       </c>
-      <c r="G61" s="8" t="inlineStr"/>
+      <c r="H61" s="8" t="inlineStr">
+        <is>
+          <t>識別號</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="5" t="inlineStr">
         <is>
+          <t>商品主檔</t>
+        </is>
+      </c>
+      <c r="B62" s="5" t="inlineStr">
+        <is>
           <t>product.template</t>
         </is>
       </c>
-      <c r="B62" s="5" t="inlineStr">
+      <c r="C62" s="5" t="inlineStr">
         <is>
           <t>char</t>
         </is>
       </c>
-      <c r="C62" s="5" t="inlineStr"/>
-      <c r="D62" s="5" t="inlineStr">
+      <c r="D62" s="5" t="inlineStr"/>
+      <c r="E62" s="5" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="E62" s="5" t="inlineStr">
+      <c r="F62" s="5" t="inlineStr">
         <is>
           <t>Name</t>
         </is>
       </c>
-      <c r="F62" s="5" t="inlineStr">
+      <c r="G62" s="5" t="inlineStr">
         <is>
           <t>名稱</t>
         </is>
       </c>
-      <c r="G62" s="6" t="inlineStr">
-        <is>
-          <t>required</t>
+      <c r="H62" s="6" t="inlineStr">
+        <is>
+          <t>名稱 · required</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="7" t="inlineStr">
         <is>
+          <t>商品主檔</t>
+        </is>
+      </c>
+      <c r="B63" s="7" t="inlineStr">
+        <is>
           <t>product.template</t>
         </is>
       </c>
-      <c r="B63" s="7" t="inlineStr">
+      <c r="C63" s="7" t="inlineStr">
         <is>
           <t>many2one</t>
         </is>
       </c>
-      <c r="C63" s="7" t="inlineStr">
+      <c r="D63" s="7" t="inlineStr">
         <is>
           <t>FK</t>
         </is>
       </c>
-      <c r="D63" s="7" t="inlineStr">
+      <c r="E63" s="7" t="inlineStr">
         <is>
           <t>uom_id</t>
         </is>
       </c>
-      <c r="E63" s="7" t="inlineStr">
+      <c r="F63" s="7" t="inlineStr">
         <is>
           <t>Unit</t>
         </is>
       </c>
-      <c r="F63" s="7" t="inlineStr">
+      <c r="G63" s="7" t="inlineStr">
         <is>
           <t>單位</t>
         </is>
       </c>
-      <c r="G63" s="8" t="inlineStr">
-        <is>
-          <t>required restrict</t>
+      <c r="H63" s="8" t="inlineStr">
+        <is>
+          <t>單位 · required restrict</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="5" t="inlineStr">
         <is>
+          <t>商品主檔</t>
+        </is>
+      </c>
+      <c r="B64" s="5" t="inlineStr">
+        <is>
           <t>product.template</t>
         </is>
       </c>
-      <c r="B64" s="5" t="inlineStr">
+      <c r="C64" s="5" t="inlineStr">
         <is>
           <t>many2one</t>
         </is>
       </c>
-      <c r="C64" s="5" t="inlineStr">
+      <c r="D64" s="5" t="inlineStr">
         <is>
           <t>FK</t>
         </is>
       </c>
-      <c r="D64" s="5" t="inlineStr">
+      <c r="E64" s="5" t="inlineStr">
         <is>
           <t>categ_id</t>
         </is>
       </c>
-      <c r="E64" s="5" t="inlineStr">
+      <c r="F64" s="5" t="inlineStr">
         <is>
           <t>Product Category</t>
         </is>
       </c>
-      <c r="F64" s="5" t="inlineStr">
+      <c r="G64" s="5" t="inlineStr">
         <is>
           <t>產品分類</t>
         </is>
       </c>
-      <c r="G64" s="6" t="inlineStr">
-        <is>
-          <t>選填 set-null</t>
+      <c r="H64" s="6" t="inlineStr">
+        <is>
+          <t>產品分類 · 選填 set-null</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="7" t="inlineStr">
         <is>
+          <t>商品主檔</t>
+        </is>
+      </c>
+      <c r="B65" s="7" t="inlineStr">
+        <is>
           <t>product.template</t>
         </is>
       </c>
-      <c r="B65" s="7" t="inlineStr">
+      <c r="C65" s="7" t="inlineStr">
         <is>
           <t>many2one</t>
         </is>
       </c>
-      <c r="C65" s="7" t="inlineStr">
+      <c r="D65" s="7" t="inlineStr">
         <is>
           <t>FK</t>
         </is>
       </c>
-      <c r="D65" s="7" t="inlineStr">
+      <c r="E65" s="7" t="inlineStr">
         <is>
           <t>company_id</t>
         </is>
       </c>
-      <c r="E65" s="7" t="inlineStr">
+      <c r="F65" s="7" t="inlineStr">
         <is>
           <t>Company</t>
         </is>
       </c>
-      <c r="F65" s="7" t="inlineStr">
+      <c r="G65" s="7" t="inlineStr">
         <is>
           <t>公司</t>
         </is>
       </c>
-      <c r="G65" s="8" t="inlineStr">
-        <is>
-          <t>選填 set-null</t>
+      <c r="H65" s="8" t="inlineStr">
+        <is>
+          <t>公司 · 選填 set-null</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="5" t="inlineStr">
         <is>
+          <t>商品主檔</t>
+        </is>
+      </c>
+      <c r="B66" s="5" t="inlineStr">
+        <is>
           <t>product.template</t>
         </is>
       </c>
-      <c r="B66" s="5" t="inlineStr">
+      <c r="C66" s="5" t="inlineStr">
         <is>
           <t>selection</t>
         </is>
       </c>
-      <c r="C66" s="5" t="inlineStr"/>
-      <c r="D66" s="5" t="inlineStr">
+      <c r="D66" s="5" t="inlineStr"/>
+      <c r="E66" s="5" t="inlineStr">
         <is>
           <t>type</t>
         </is>
       </c>
-      <c r="E66" s="5" t="inlineStr">
+      <c r="F66" s="5" t="inlineStr">
         <is>
           <t>Product Type</t>
         </is>
       </c>
-      <c r="F66" s="5" t="inlineStr">
+      <c r="G66" s="5" t="inlineStr">
         <is>
           <t>產品類型</t>
         </is>
       </c>
-      <c r="G66" s="6" t="inlineStr">
-        <is>
-          <t>required</t>
+      <c r="H66" s="6" t="inlineStr">
+        <is>
+          <t>產品類型 · required</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="7" t="inlineStr">
         <is>
+          <t>商品主檔</t>
+        </is>
+      </c>
+      <c r="B67" s="7" t="inlineStr">
+        <is>
           <t>product.template</t>
         </is>
       </c>
-      <c r="B67" s="7" t="inlineStr">
+      <c r="C67" s="7" t="inlineStr">
         <is>
           <t>selection</t>
         </is>
       </c>
-      <c r="C67" s="7" t="inlineStr"/>
-      <c r="D67" s="7" t="inlineStr">
+      <c r="D67" s="7" t="inlineStr"/>
+      <c r="E67" s="7" t="inlineStr">
         <is>
           <t>tracking</t>
         </is>
       </c>
-      <c r="E67" s="7" t="inlineStr">
+      <c r="F67" s="7" t="inlineStr">
         <is>
           <t>Tracking</t>
         </is>
       </c>
-      <c r="F67" s="7" t="inlineStr">
+      <c r="G67" s="7" t="inlineStr">
         <is>
           <t>追蹤</t>
         </is>
       </c>
-      <c r="G67" s="8" t="inlineStr">
-        <is>
-          <t>required</t>
+      <c r="H67" s="8" t="inlineStr">
+        <is>
+          <t>追蹤 · required</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="5" t="inlineStr">
         <is>
+          <t>商品主檔</t>
+        </is>
+      </c>
+      <c r="B68" s="5" t="inlineStr">
+        <is>
           <t>product.template</t>
         </is>
       </c>
-      <c r="B68" s="5" t="inlineStr">
+      <c r="C68" s="5" t="inlineStr">
         <is>
           <t>selection</t>
         </is>
       </c>
-      <c r="C68" s="5" t="inlineStr"/>
-      <c r="D68" s="5" t="inlineStr">
+      <c r="D68" s="5" t="inlineStr"/>
+      <c r="E68" s="5" t="inlineStr">
         <is>
           <t>service_tracking</t>
         </is>
       </c>
-      <c r="E68" s="5" t="inlineStr">
+      <c r="F68" s="5" t="inlineStr">
         <is>
           <t>Create on Order</t>
         </is>
       </c>
-      <c r="F68" s="5" t="inlineStr">
+      <c r="G68" s="5" t="inlineStr">
         <is>
           <t>由訂單建立</t>
         </is>
       </c>
-      <c r="G68" s="6" t="inlineStr">
-        <is>
-          <t>required</t>
+      <c r="H68" s="6" t="inlineStr">
+        <is>
+          <t>由訂單建立 · required</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="7" t="inlineStr">
         <is>
+          <t>商品主檔</t>
+        </is>
+      </c>
+      <c r="B69" s="7" t="inlineStr">
+        <is>
           <t>product.product</t>
         </is>
       </c>
-      <c r="B69" s="7" t="inlineStr">
+      <c r="C69" s="7" t="inlineStr">
         <is>
           <t>integer</t>
         </is>
       </c>
-      <c r="C69" s="7" t="inlineStr">
+      <c r="D69" s="7" t="inlineStr">
         <is>
           <t>PK</t>
         </is>
       </c>
-      <c r="D69" s="7" t="inlineStr">
+      <c r="E69" s="7" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="E69" s="7" t="inlineStr">
+      <c r="F69" s="7" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="F69" s="7" t="inlineStr">
+      <c r="G69" s="7" t="inlineStr">
         <is>
           <t>識別號</t>
         </is>
       </c>
-      <c r="G69" s="8" t="inlineStr"/>
+      <c r="H69" s="8" t="inlineStr">
+        <is>
+          <t>識別號</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="5" t="inlineStr">
         <is>
+          <t>商品主檔</t>
+        </is>
+      </c>
+      <c r="B70" s="5" t="inlineStr">
+        <is>
           <t>product.product</t>
         </is>
       </c>
-      <c r="B70" s="5" t="inlineStr">
+      <c r="C70" s="5" t="inlineStr">
         <is>
           <t>many2one</t>
         </is>
       </c>
-      <c r="C70" s="5" t="inlineStr">
+      <c r="D70" s="5" t="inlineStr">
         <is>
           <t>FK</t>
         </is>
       </c>
-      <c r="D70" s="5" t="inlineStr">
+      <c r="E70" s="5" t="inlineStr">
         <is>
           <t>product_tmpl_id</t>
         </is>
       </c>
-      <c r="E70" s="5" t="inlineStr">
+      <c r="F70" s="5" t="inlineStr">
         <is>
           <t>Product Template</t>
         </is>
       </c>
-      <c r="F70" s="5" t="inlineStr">
+      <c r="G70" s="5" t="inlineStr">
         <is>
           <t>產品模板</t>
         </is>
       </c>
-      <c r="G70" s="6" t="inlineStr">
-        <is>
-          <t>required cascade</t>
+      <c r="H70" s="6" t="inlineStr">
+        <is>
+          <t>產品模板 · required cascade</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="7" t="inlineStr">
         <is>
+          <t>商品主檔</t>
+        </is>
+      </c>
+      <c r="B71" s="7" t="inlineStr">
+        <is>
           <t>product.category</t>
         </is>
       </c>
-      <c r="B71" s="7" t="inlineStr">
+      <c r="C71" s="7" t="inlineStr">
         <is>
           <t>integer</t>
         </is>
       </c>
-      <c r="C71" s="7" t="inlineStr">
+      <c r="D71" s="7" t="inlineStr">
         <is>
           <t>PK</t>
         </is>
       </c>
-      <c r="D71" s="7" t="inlineStr">
+      <c r="E71" s="7" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="E71" s="7" t="inlineStr">
+      <c r="F71" s="7" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="F71" s="7" t="inlineStr">
+      <c r="G71" s="7" t="inlineStr">
         <is>
           <t>識別號</t>
         </is>
       </c>
-      <c r="G71" s="8" t="inlineStr"/>
+      <c r="H71" s="8" t="inlineStr">
+        <is>
+          <t>識別號</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="5" t="inlineStr">
         <is>
+          <t>商品主檔</t>
+        </is>
+      </c>
+      <c r="B72" s="5" t="inlineStr">
+        <is>
           <t>product.category</t>
         </is>
       </c>
-      <c r="B72" s="5" t="inlineStr">
+      <c r="C72" s="5" t="inlineStr">
         <is>
           <t>char</t>
         </is>
       </c>
-      <c r="C72" s="5" t="inlineStr"/>
-      <c r="D72" s="5" t="inlineStr">
+      <c r="D72" s="5" t="inlineStr"/>
+      <c r="E72" s="5" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="E72" s="5" t="inlineStr">
+      <c r="F72" s="5" t="inlineStr">
         <is>
           <t>Name</t>
         </is>
       </c>
-      <c r="F72" s="5" t="inlineStr">
+      <c r="G72" s="5" t="inlineStr">
         <is>
           <t>名稱</t>
         </is>
       </c>
-      <c r="G72" s="6" t="inlineStr">
-        <is>
-          <t>required</t>
+      <c r="H72" s="6" t="inlineStr">
+        <is>
+          <t>名稱 · required</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="7" t="inlineStr">
         <is>
+          <t>商品主檔</t>
+        </is>
+      </c>
+      <c r="B73" s="7" t="inlineStr">
+        <is>
           <t>product.category</t>
         </is>
       </c>
-      <c r="B73" s="7" t="inlineStr">
+      <c r="C73" s="7" t="inlineStr">
         <is>
           <t>many2one</t>
         </is>
       </c>
-      <c r="C73" s="7" t="inlineStr">
+      <c r="D73" s="7" t="inlineStr">
         <is>
           <t>FK</t>
         </is>
       </c>
-      <c r="D73" s="7" t="inlineStr">
+      <c r="E73" s="7" t="inlineStr">
         <is>
           <t>parent_id</t>
         </is>
       </c>
-      <c r="E73" s="7" t="inlineStr">
+      <c r="F73" s="7" t="inlineStr">
         <is>
           <t>Parent Category</t>
         </is>
       </c>
-      <c r="F73" s="7" t="inlineStr">
+      <c r="G73" s="7" t="inlineStr">
         <is>
           <t>上級類別</t>
         </is>
       </c>
-      <c r="G73" s="8" t="inlineStr">
-        <is>
-          <t>自身 cascade</t>
+      <c r="H73" s="8" t="inlineStr">
+        <is>
+          <t>上級類別 · 自身 cascade</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="5" t="inlineStr">
         <is>
+          <t>商品主檔</t>
+        </is>
+      </c>
+      <c r="B74" s="5" t="inlineStr">
+        <is>
           <t>uom.uom</t>
         </is>
       </c>
-      <c r="B74" s="5" t="inlineStr">
+      <c r="C74" s="5" t="inlineStr">
         <is>
           <t>integer</t>
         </is>
       </c>
-      <c r="C74" s="5" t="inlineStr">
+      <c r="D74" s="5" t="inlineStr">
         <is>
           <t>PK</t>
         </is>
       </c>
-      <c r="D74" s="5" t="inlineStr">
+      <c r="E74" s="5" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="E74" s="5" t="inlineStr">
+      <c r="F74" s="5" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="F74" s="5" t="inlineStr">
+      <c r="G74" s="5" t="inlineStr">
         <is>
           <t>識別號</t>
         </is>
       </c>
-      <c r="G74" s="6" t="inlineStr"/>
+      <c r="H74" s="6" t="inlineStr">
+        <is>
+          <t>識別號</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="7" t="inlineStr">
         <is>
+          <t>商品主檔</t>
+        </is>
+      </c>
+      <c r="B75" s="7" t="inlineStr">
+        <is>
           <t>uom.uom</t>
         </is>
       </c>
-      <c r="B75" s="7" t="inlineStr">
+      <c r="C75" s="7" t="inlineStr">
         <is>
           <t>char</t>
         </is>
       </c>
-      <c r="C75" s="7" t="inlineStr"/>
-      <c r="D75" s="7" t="inlineStr">
+      <c r="D75" s="7" t="inlineStr"/>
+      <c r="E75" s="7" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="E75" s="7" t="inlineStr">
+      <c r="F75" s="7" t="inlineStr">
         <is>
           <t>Unit Name</t>
         </is>
       </c>
-      <c r="F75" s="7" t="inlineStr">
+      <c r="G75" s="7" t="inlineStr">
         <is>
           <t>單位名稱</t>
         </is>
       </c>
-      <c r="G75" s="8" t="inlineStr">
-        <is>
-          <t>required</t>
+      <c r="H75" s="8" t="inlineStr">
+        <is>
+          <t>單位名稱 · required</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="5" t="inlineStr">
         <is>
+          <t>商品主檔</t>
+        </is>
+      </c>
+      <c r="B76" s="5" t="inlineStr">
+        <is>
           <t>uom.uom</t>
         </is>
       </c>
-      <c r="B76" s="5" t="inlineStr">
+      <c r="C76" s="5" t="inlineStr">
         <is>
           <t>float</t>
         </is>
       </c>
-      <c r="C76" s="5" t="inlineStr"/>
-      <c r="D76" s="5" t="inlineStr">
+      <c r="D76" s="5" t="inlineStr"/>
+      <c r="E76" s="5" t="inlineStr">
         <is>
           <t>relative_factor</t>
         </is>
       </c>
-      <c r="E76" s="5" t="inlineStr">
+      <c r="F76" s="5" t="inlineStr">
         <is>
           <t>Contains</t>
         </is>
       </c>
-      <c r="F76" s="5" t="inlineStr">
+      <c r="G76" s="5" t="inlineStr">
         <is>
           <t>包含</t>
         </is>
       </c>
-      <c r="G76" s="6" t="inlineStr">
-        <is>
-          <t>required</t>
+      <c r="H76" s="6" t="inlineStr">
+        <is>
+          <t>包含 · required</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="7" t="inlineStr">
         <is>
+          <t>商品主檔</t>
+        </is>
+      </c>
+      <c r="B77" s="7" t="inlineStr">
+        <is>
           <t>uom.uom</t>
         </is>
       </c>
-      <c r="B77" s="7" t="inlineStr">
+      <c r="C77" s="7" t="inlineStr">
         <is>
           <t>many2one</t>
         </is>
       </c>
-      <c r="C77" s="7" t="inlineStr">
+      <c r="D77" s="7" t="inlineStr">
         <is>
           <t>FK</t>
         </is>
       </c>
-      <c r="D77" s="7" t="inlineStr">
+      <c r="E77" s="7" t="inlineStr">
         <is>
           <t>relative_uom_id</t>
         </is>
       </c>
-      <c r="E77" s="7" t="inlineStr">
+      <c r="F77" s="7" t="inlineStr">
         <is>
           <t>Reference Unit</t>
         </is>
       </c>
-      <c r="F77" s="7" t="inlineStr">
+      <c r="G77" s="7" t="inlineStr">
         <is>
           <t>參考單位</t>
         </is>
       </c>
-      <c r="G77" s="8" t="inlineStr">
-        <is>
-          <t>自身 cascade</t>
+      <c r="H77" s="8" t="inlineStr">
+        <is>
+          <t>參考單位 · 自身 cascade</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="5" t="inlineStr">
         <is>
+          <t>商品主檔</t>
+        </is>
+      </c>
+      <c r="B78" s="5" t="inlineStr">
+        <is>
           <t>uom.uom</t>
         </is>
       </c>
-      <c r="B78" s="5" t="inlineStr">
+      <c r="C78" s="5" t="inlineStr">
         <is>
           <t>float</t>
         </is>
       </c>
-      <c r="C78" s="5" t="inlineStr"/>
-      <c r="D78" s="5" t="inlineStr">
+      <c r="D78" s="5" t="inlineStr"/>
+      <c r="E78" s="5" t="inlineStr">
         <is>
           <t>factor</t>
         </is>
       </c>
-      <c r="E78" s="5" t="inlineStr">
+      <c r="F78" s="5" t="inlineStr">
         <is>
           <t>Absolute Quantity</t>
         </is>
       </c>
-      <c r="F78" s="5" t="inlineStr">
+      <c r="G78" s="5" t="inlineStr">
         <is>
           <t>絕對數量</t>
         </is>
       </c>
-      <c r="G78" s="6" t="inlineStr">
+      <c r="H78" s="6" t="inlineStr">
         <is>
           <t>絕對數量</t>
         </is>
@@ -3345,941 +3824,1100 @@
     <row r="79">
       <c r="A79" s="7" t="inlineStr">
         <is>
+          <t>商品主檔</t>
+        </is>
+      </c>
+      <c r="B79" s="7" t="inlineStr">
+        <is>
           <t>uom.uom</t>
         </is>
       </c>
-      <c r="B79" s="7" t="inlineStr">
+      <c r="C79" s="7" t="inlineStr">
         <is>
           <t>char</t>
         </is>
       </c>
-      <c r="C79" s="7" t="inlineStr"/>
-      <c r="D79" s="7" t="inlineStr">
+      <c r="D79" s="7" t="inlineStr"/>
+      <c r="E79" s="7" t="inlineStr">
         <is>
           <t>parent_path</t>
         </is>
       </c>
-      <c r="E79" s="7" t="inlineStr">
+      <c r="F79" s="7" t="inlineStr">
         <is>
           <t>Parent Path</t>
         </is>
       </c>
-      <c r="F79" s="7" t="inlineStr">
+      <c r="G79" s="7" t="inlineStr">
         <is>
           <t>上級路徑</t>
         </is>
       </c>
-      <c r="G79" s="8" t="inlineStr">
-        <is>
-          <t>階層索引</t>
+      <c r="H79" s="8" t="inlineStr">
+        <is>
+          <t>上級路徑 · 階層索引</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="5" t="inlineStr">
         <is>
+          <t>商品主檔</t>
+        </is>
+      </c>
+      <c r="B80" s="5" t="inlineStr">
+        <is>
           <t>product.uom</t>
         </is>
       </c>
-      <c r="B80" s="5" t="inlineStr">
+      <c r="C80" s="5" t="inlineStr">
         <is>
           <t>integer</t>
         </is>
       </c>
-      <c r="C80" s="5" t="inlineStr">
+      <c r="D80" s="5" t="inlineStr">
         <is>
           <t>PK</t>
         </is>
       </c>
-      <c r="D80" s="5" t="inlineStr">
+      <c r="E80" s="5" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="E80" s="5" t="inlineStr">
+      <c r="F80" s="5" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="F80" s="5" t="inlineStr">
+      <c r="G80" s="5" t="inlineStr">
         <is>
           <t>識別號</t>
         </is>
       </c>
-      <c r="G80" s="6" t="inlineStr"/>
+      <c r="H80" s="6" t="inlineStr">
+        <is>
+          <t>識別號</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="7" t="inlineStr">
         <is>
+          <t>商品主檔</t>
+        </is>
+      </c>
+      <c r="B81" s="7" t="inlineStr">
+        <is>
           <t>product.uom</t>
         </is>
       </c>
-      <c r="B81" s="7" t="inlineStr">
+      <c r="C81" s="7" t="inlineStr">
         <is>
           <t>char</t>
         </is>
       </c>
-      <c r="C81" s="7" t="inlineStr"/>
-      <c r="D81" s="7" t="inlineStr">
+      <c r="D81" s="7" t="inlineStr"/>
+      <c r="E81" s="7" t="inlineStr">
         <is>
           <t>barcode</t>
         </is>
       </c>
-      <c r="E81" s="7" t="inlineStr">
+      <c r="F81" s="7" t="inlineStr">
         <is>
           <t>Barcode</t>
         </is>
       </c>
-      <c r="F81" s="7" t="inlineStr">
+      <c r="G81" s="7" t="inlineStr">
         <is>
           <t>條碼</t>
         </is>
       </c>
-      <c r="G81" s="8" t="inlineStr">
-        <is>
-          <t>required</t>
+      <c r="H81" s="8" t="inlineStr">
+        <is>
+          <t>條碼 · required</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="5" t="inlineStr">
         <is>
+          <t>商品主檔</t>
+        </is>
+      </c>
+      <c r="B82" s="5" t="inlineStr">
+        <is>
           <t>product.uom</t>
         </is>
       </c>
-      <c r="B82" s="5" t="inlineStr">
+      <c r="C82" s="5" t="inlineStr">
         <is>
           <t>many2one</t>
         </is>
       </c>
-      <c r="C82" s="5" t="inlineStr">
+      <c r="D82" s="5" t="inlineStr">
         <is>
           <t>FK</t>
         </is>
       </c>
-      <c r="D82" s="5" t="inlineStr">
+      <c r="E82" s="5" t="inlineStr">
         <is>
           <t>product_id</t>
         </is>
       </c>
-      <c r="E82" s="5" t="inlineStr">
+      <c r="F82" s="5" t="inlineStr">
         <is>
           <t>Product</t>
         </is>
       </c>
-      <c r="F82" s="5" t="inlineStr">
+      <c r="G82" s="5" t="inlineStr">
         <is>
           <t>商品</t>
         </is>
       </c>
-      <c r="G82" s="6" t="inlineStr">
-        <is>
-          <t>required cascade</t>
+      <c r="H82" s="6" t="inlineStr">
+        <is>
+          <t>商品 · required cascade</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="7" t="inlineStr">
         <is>
+          <t>商品主檔</t>
+        </is>
+      </c>
+      <c r="B83" s="7" t="inlineStr">
+        <is>
           <t>product.uom</t>
         </is>
       </c>
-      <c r="B83" s="7" t="inlineStr">
+      <c r="C83" s="7" t="inlineStr">
         <is>
           <t>many2one</t>
         </is>
       </c>
-      <c r="C83" s="7" t="inlineStr">
+      <c r="D83" s="7" t="inlineStr">
         <is>
           <t>FK</t>
         </is>
       </c>
-      <c r="D83" s="7" t="inlineStr">
+      <c r="E83" s="7" t="inlineStr">
         <is>
           <t>uom_id</t>
         </is>
       </c>
-      <c r="E83" s="7" t="inlineStr">
+      <c r="F83" s="7" t="inlineStr">
         <is>
           <t>Unit</t>
         </is>
       </c>
-      <c r="F83" s="7" t="inlineStr">
+      <c r="G83" s="7" t="inlineStr">
         <is>
           <t>單位</t>
         </is>
       </c>
-      <c r="G83" s="8" t="inlineStr">
-        <is>
-          <t>required cascade</t>
+      <c r="H83" s="8" t="inlineStr">
+        <is>
+          <t>單位 · required cascade</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="5" t="inlineStr">
         <is>
+          <t>商品主檔</t>
+        </is>
+      </c>
+      <c r="B84" s="5" t="inlineStr">
+        <is>
           <t>product.supplierinfo</t>
         </is>
       </c>
-      <c r="B84" s="5" t="inlineStr">
+      <c r="C84" s="5" t="inlineStr">
         <is>
           <t>integer</t>
         </is>
       </c>
-      <c r="C84" s="5" t="inlineStr">
+      <c r="D84" s="5" t="inlineStr">
         <is>
           <t>PK</t>
         </is>
       </c>
-      <c r="D84" s="5" t="inlineStr">
+      <c r="E84" s="5" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="E84" s="5" t="inlineStr">
+      <c r="F84" s="5" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="F84" s="5" t="inlineStr">
+      <c r="G84" s="5" t="inlineStr">
         <is>
           <t>識別號</t>
         </is>
       </c>
-      <c r="G84" s="6" t="inlineStr"/>
+      <c r="H84" s="6" t="inlineStr">
+        <is>
+          <t>識別號</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="7" t="inlineStr">
         <is>
+          <t>商品主檔</t>
+        </is>
+      </c>
+      <c r="B85" s="7" t="inlineStr">
+        <is>
           <t>product.supplierinfo</t>
         </is>
       </c>
-      <c r="B85" s="7" t="inlineStr">
+      <c r="C85" s="7" t="inlineStr">
         <is>
           <t>many2one</t>
         </is>
       </c>
-      <c r="C85" s="7" t="inlineStr">
+      <c r="D85" s="7" t="inlineStr">
         <is>
           <t>FK</t>
         </is>
       </c>
-      <c r="D85" s="7" t="inlineStr">
+      <c r="E85" s="7" t="inlineStr">
         <is>
           <t>partner_id</t>
         </is>
       </c>
-      <c r="E85" s="7" t="inlineStr">
+      <c r="F85" s="7" t="inlineStr">
         <is>
           <t>Vendor</t>
         </is>
       </c>
-      <c r="F85" s="7" t="inlineStr">
+      <c r="G85" s="7" t="inlineStr">
         <is>
           <t>供應商</t>
         </is>
       </c>
-      <c r="G85" s="8" t="inlineStr">
-        <is>
-          <t>required cascade</t>
+      <c r="H85" s="8" t="inlineStr">
+        <is>
+          <t>供應商 · required cascade</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="5" t="inlineStr">
         <is>
+          <t>商品主檔</t>
+        </is>
+      </c>
+      <c r="B86" s="5" t="inlineStr">
+        <is>
           <t>product.supplierinfo</t>
         </is>
       </c>
-      <c r="B86" s="5" t="inlineStr">
+      <c r="C86" s="5" t="inlineStr">
         <is>
           <t>many2one</t>
         </is>
       </c>
-      <c r="C86" s="5" t="inlineStr">
+      <c r="D86" s="5" t="inlineStr">
         <is>
           <t>FK</t>
         </is>
       </c>
-      <c r="D86" s="5" t="inlineStr">
+      <c r="E86" s="5" t="inlineStr">
         <is>
           <t>product_tmpl_id</t>
         </is>
       </c>
-      <c r="E86" s="5" t="inlineStr">
+      <c r="F86" s="5" t="inlineStr">
         <is>
           <t>Product Template</t>
         </is>
       </c>
-      <c r="F86" s="5" t="inlineStr">
+      <c r="G86" s="5" t="inlineStr">
         <is>
           <t>產品模板</t>
         </is>
       </c>
-      <c r="G86" s="6" t="inlineStr">
-        <is>
-          <t>required cascade</t>
+      <c r="H86" s="6" t="inlineStr">
+        <is>
+          <t>產品模板 · required cascade</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="7" t="inlineStr">
         <is>
+          <t>商品主檔</t>
+        </is>
+      </c>
+      <c r="B87" s="7" t="inlineStr">
+        <is>
           <t>product.supplierinfo</t>
         </is>
       </c>
-      <c r="B87" s="7" t="inlineStr">
+      <c r="C87" s="7" t="inlineStr">
         <is>
           <t>many2one</t>
         </is>
       </c>
-      <c r="C87" s="7" t="inlineStr">
+      <c r="D87" s="7" t="inlineStr">
         <is>
           <t>FK</t>
         </is>
       </c>
-      <c r="D87" s="7" t="inlineStr">
+      <c r="E87" s="7" t="inlineStr">
         <is>
           <t>product_uom_id</t>
         </is>
       </c>
-      <c r="E87" s="7" t="inlineStr">
+      <c r="F87" s="7" t="inlineStr">
         <is>
           <t>Unit</t>
         </is>
       </c>
-      <c r="F87" s="7" t="inlineStr">
+      <c r="G87" s="7" t="inlineStr">
         <is>
           <t>單位</t>
         </is>
       </c>
-      <c r="G87" s="8" t="inlineStr">
-        <is>
-          <t>required restrict</t>
+      <c r="H87" s="8" t="inlineStr">
+        <is>
+          <t>單位 · required restrict</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="5" t="inlineStr">
         <is>
+          <t>商品主檔</t>
+        </is>
+      </c>
+      <c r="B88" s="5" t="inlineStr">
+        <is>
           <t>product.supplierinfo</t>
         </is>
       </c>
-      <c r="B88" s="5" t="inlineStr">
+      <c r="C88" s="5" t="inlineStr">
         <is>
           <t>many2one</t>
         </is>
       </c>
-      <c r="C88" s="5" t="inlineStr">
+      <c r="D88" s="5" t="inlineStr">
         <is>
           <t>FK</t>
         </is>
       </c>
-      <c r="D88" s="5" t="inlineStr">
+      <c r="E88" s="5" t="inlineStr">
         <is>
           <t>currency_id</t>
         </is>
       </c>
-      <c r="E88" s="5" t="inlineStr">
+      <c r="F88" s="5" t="inlineStr">
         <is>
           <t>Currency</t>
         </is>
       </c>
-      <c r="F88" s="5" t="inlineStr">
+      <c r="G88" s="5" t="inlineStr">
         <is>
           <t>貨幣</t>
         </is>
       </c>
-      <c r="G88" s="6" t="inlineStr">
-        <is>
-          <t>required restrict 圖外</t>
+      <c r="H88" s="6" t="inlineStr">
+        <is>
+          <t>貨幣 · required restrict 圖外</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="7" t="inlineStr">
         <is>
+          <t>商品主檔</t>
+        </is>
+      </c>
+      <c r="B89" s="7" t="inlineStr">
+        <is>
           <t>product.supplierinfo</t>
         </is>
       </c>
-      <c r="B89" s="7" t="inlineStr">
+      <c r="C89" s="7" t="inlineStr">
         <is>
           <t>many2one</t>
         </is>
       </c>
-      <c r="C89" s="7" t="inlineStr">
+      <c r="D89" s="7" t="inlineStr">
         <is>
           <t>FK</t>
         </is>
       </c>
-      <c r="D89" s="7" t="inlineStr">
+      <c r="E89" s="7" t="inlineStr">
         <is>
           <t>product_id</t>
         </is>
       </c>
-      <c r="E89" s="7" t="inlineStr">
+      <c r="F89" s="7" t="inlineStr">
         <is>
           <t>Product Variant</t>
         </is>
       </c>
-      <c r="F89" s="7" t="inlineStr">
+      <c r="G89" s="7" t="inlineStr">
         <is>
           <t>產品款式</t>
         </is>
       </c>
-      <c r="G89" s="8" t="inlineStr">
-        <is>
-          <t>選填 set-null</t>
+      <c r="H89" s="8" t="inlineStr">
+        <is>
+          <t>產品款式 · 選填 set-null</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="5" t="inlineStr">
         <is>
+          <t>商品主檔</t>
+        </is>
+      </c>
+      <c r="B90" s="5" t="inlineStr">
+        <is>
           <t>product.supplierinfo</t>
         </is>
       </c>
-      <c r="B90" s="5" t="inlineStr">
+      <c r="C90" s="5" t="inlineStr">
         <is>
           <t>float</t>
         </is>
       </c>
-      <c r="C90" s="5" t="inlineStr"/>
-      <c r="D90" s="5" t="inlineStr">
+      <c r="D90" s="5" t="inlineStr"/>
+      <c r="E90" s="5" t="inlineStr">
         <is>
           <t>min_qty</t>
         </is>
       </c>
-      <c r="E90" s="5" t="inlineStr">
+      <c r="F90" s="5" t="inlineStr">
         <is>
           <t>Quantity</t>
         </is>
       </c>
-      <c r="F90" s="5" t="inlineStr">
+      <c r="G90" s="5" t="inlineStr">
         <is>
           <t>數量</t>
         </is>
       </c>
-      <c r="G90" s="6" t="inlineStr">
-        <is>
-          <t>required</t>
+      <c r="H90" s="6" t="inlineStr">
+        <is>
+          <t>數量 · required</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="7" t="inlineStr">
         <is>
+          <t>商品主檔</t>
+        </is>
+      </c>
+      <c r="B91" s="7" t="inlineStr">
+        <is>
           <t>product.supplierinfo</t>
         </is>
       </c>
-      <c r="B91" s="7" t="inlineStr">
+      <c r="C91" s="7" t="inlineStr">
         <is>
           <t>integer</t>
         </is>
       </c>
-      <c r="C91" s="7" t="inlineStr"/>
-      <c r="D91" s="7" t="inlineStr">
+      <c r="D91" s="7" t="inlineStr"/>
+      <c r="E91" s="7" t="inlineStr">
         <is>
           <t>delay</t>
         </is>
       </c>
-      <c r="E91" s="7" t="inlineStr">
+      <c r="F91" s="7" t="inlineStr">
         <is>
           <t>Lead Time</t>
         </is>
       </c>
-      <c r="F91" s="7" t="inlineStr">
+      <c r="G91" s="7" t="inlineStr">
         <is>
           <t>前置時間</t>
         </is>
       </c>
-      <c r="G91" s="8" t="inlineStr">
-        <is>
-          <t>required</t>
+      <c r="H91" s="8" t="inlineStr">
+        <is>
+          <t>前置時間 · required</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="5" t="inlineStr">
         <is>
+          <t>商品主檔</t>
+        </is>
+      </c>
+      <c r="B92" s="5" t="inlineStr">
+        <is>
           <t>product.attribute</t>
         </is>
       </c>
-      <c r="B92" s="5" t="inlineStr">
+      <c r="C92" s="5" t="inlineStr">
         <is>
           <t>integer</t>
         </is>
       </c>
-      <c r="C92" s="5" t="inlineStr">
+      <c r="D92" s="5" t="inlineStr">
         <is>
           <t>PK</t>
         </is>
       </c>
-      <c r="D92" s="5" t="inlineStr">
+      <c r="E92" s="5" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="E92" s="5" t="inlineStr">
+      <c r="F92" s="5" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="F92" s="5" t="inlineStr">
+      <c r="G92" s="5" t="inlineStr">
         <is>
           <t>識別號</t>
         </is>
       </c>
-      <c r="G92" s="6" t="inlineStr"/>
+      <c r="H92" s="6" t="inlineStr">
+        <is>
+          <t>識別號</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" s="7" t="inlineStr">
         <is>
+          <t>商品主檔</t>
+        </is>
+      </c>
+      <c r="B93" s="7" t="inlineStr">
+        <is>
           <t>product.attribute</t>
         </is>
       </c>
-      <c r="B93" s="7" t="inlineStr">
+      <c r="C93" s="7" t="inlineStr">
         <is>
           <t>char</t>
         </is>
       </c>
-      <c r="C93" s="7" t="inlineStr"/>
-      <c r="D93" s="7" t="inlineStr">
+      <c r="D93" s="7" t="inlineStr"/>
+      <c r="E93" s="7" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="E93" s="7" t="inlineStr">
+      <c r="F93" s="7" t="inlineStr">
         <is>
           <t>Attribute</t>
         </is>
       </c>
-      <c r="F93" s="7" t="inlineStr">
+      <c r="G93" s="7" t="inlineStr">
         <is>
           <t>屬性</t>
         </is>
       </c>
-      <c r="G93" s="8" t="inlineStr">
-        <is>
-          <t>required</t>
+      <c r="H93" s="8" t="inlineStr">
+        <is>
+          <t>屬性 · required</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="5" t="inlineStr">
         <is>
+          <t>商品主檔</t>
+        </is>
+      </c>
+      <c r="B94" s="5" t="inlineStr">
+        <is>
           <t>product.attribute</t>
         </is>
       </c>
-      <c r="B94" s="5" t="inlineStr">
+      <c r="C94" s="5" t="inlineStr">
         <is>
           <t>selection</t>
         </is>
       </c>
-      <c r="C94" s="5" t="inlineStr"/>
-      <c r="D94" s="5" t="inlineStr">
+      <c r="D94" s="5" t="inlineStr"/>
+      <c r="E94" s="5" t="inlineStr">
         <is>
           <t>create_variant</t>
         </is>
       </c>
-      <c r="E94" s="5" t="inlineStr">
+      <c r="F94" s="5" t="inlineStr">
         <is>
           <t>Variant Creation</t>
         </is>
       </c>
-      <c r="F94" s="5" t="inlineStr">
+      <c r="G94" s="5" t="inlineStr">
         <is>
           <t>建立款式變體</t>
         </is>
       </c>
-      <c r="G94" s="6" t="inlineStr">
-        <is>
-          <t>required</t>
+      <c r="H94" s="6" t="inlineStr">
+        <is>
+          <t>建立款式變體 · required</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="7" t="inlineStr">
         <is>
+          <t>商品主檔</t>
+        </is>
+      </c>
+      <c r="B95" s="7" t="inlineStr">
+        <is>
           <t>product.attribute</t>
         </is>
       </c>
-      <c r="B95" s="7" t="inlineStr">
+      <c r="C95" s="7" t="inlineStr">
         <is>
           <t>selection</t>
         </is>
       </c>
-      <c r="C95" s="7" t="inlineStr"/>
-      <c r="D95" s="7" t="inlineStr">
+      <c r="D95" s="7" t="inlineStr"/>
+      <c r="E95" s="7" t="inlineStr">
         <is>
           <t>display_type</t>
         </is>
       </c>
-      <c r="E95" s="7" t="inlineStr">
+      <c r="F95" s="7" t="inlineStr">
         <is>
           <t>Display Type</t>
         </is>
       </c>
-      <c r="F95" s="7" t="inlineStr">
+      <c r="G95" s="7" t="inlineStr">
         <is>
           <t>顯示類型</t>
         </is>
       </c>
-      <c r="G95" s="8" t="inlineStr">
-        <is>
-          <t>required</t>
+      <c r="H95" s="8" t="inlineStr">
+        <is>
+          <t>顯示類型 · required</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="5" t="inlineStr">
         <is>
+          <t>商品主檔</t>
+        </is>
+      </c>
+      <c r="B96" s="5" t="inlineStr">
+        <is>
           <t>product.attribute.value</t>
         </is>
       </c>
-      <c r="B96" s="5" t="inlineStr">
+      <c r="C96" s="5" t="inlineStr">
         <is>
           <t>integer</t>
         </is>
       </c>
-      <c r="C96" s="5" t="inlineStr">
+      <c r="D96" s="5" t="inlineStr">
         <is>
           <t>PK</t>
         </is>
       </c>
-      <c r="D96" s="5" t="inlineStr">
+      <c r="E96" s="5" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="E96" s="5" t="inlineStr">
+      <c r="F96" s="5" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="F96" s="5" t="inlineStr">
+      <c r="G96" s="5" t="inlineStr">
         <is>
           <t>識別號</t>
         </is>
       </c>
-      <c r="G96" s="6" t="inlineStr"/>
+      <c r="H96" s="6" t="inlineStr">
+        <is>
+          <t>識別號</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" s="7" t="inlineStr">
         <is>
+          <t>商品主檔</t>
+        </is>
+      </c>
+      <c r="B97" s="7" t="inlineStr">
+        <is>
           <t>product.attribute.value</t>
         </is>
       </c>
-      <c r="B97" s="7" t="inlineStr">
+      <c r="C97" s="7" t="inlineStr">
         <is>
           <t>char</t>
         </is>
       </c>
-      <c r="C97" s="7" t="inlineStr"/>
-      <c r="D97" s="7" t="inlineStr">
+      <c r="D97" s="7" t="inlineStr"/>
+      <c r="E97" s="7" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="E97" s="7" t="inlineStr">
+      <c r="F97" s="7" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
       </c>
-      <c r="F97" s="7" t="inlineStr">
+      <c r="G97" s="7" t="inlineStr">
         <is>
           <t>值</t>
         </is>
       </c>
-      <c r="G97" s="8" t="inlineStr">
-        <is>
-          <t>required</t>
+      <c r="H97" s="8" t="inlineStr">
+        <is>
+          <t>值 · required</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="5" t="inlineStr">
         <is>
+          <t>商品主檔</t>
+        </is>
+      </c>
+      <c r="B98" s="5" t="inlineStr">
+        <is>
           <t>product.attribute.value</t>
         </is>
       </c>
-      <c r="B98" s="5" t="inlineStr">
+      <c r="C98" s="5" t="inlineStr">
         <is>
           <t>many2one</t>
         </is>
       </c>
-      <c r="C98" s="5" t="inlineStr">
+      <c r="D98" s="5" t="inlineStr">
         <is>
           <t>FK</t>
         </is>
       </c>
-      <c r="D98" s="5" t="inlineStr">
+      <c r="E98" s="5" t="inlineStr">
         <is>
           <t>attribute_id</t>
         </is>
       </c>
-      <c r="E98" s="5" t="inlineStr">
+      <c r="F98" s="5" t="inlineStr">
         <is>
           <t>Attribute</t>
         </is>
       </c>
-      <c r="F98" s="5" t="inlineStr">
+      <c r="G98" s="5" t="inlineStr">
         <is>
           <t>屬性</t>
         </is>
       </c>
-      <c r="G98" s="6" t="inlineStr">
-        <is>
-          <t>required cascade</t>
+      <c r="H98" s="6" t="inlineStr">
+        <is>
+          <t>屬性 · required cascade</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="7" t="inlineStr">
         <is>
+          <t>商品主檔</t>
+        </is>
+      </c>
+      <c r="B99" s="7" t="inlineStr">
+        <is>
           <t>product.template.attribute.line</t>
         </is>
       </c>
-      <c r="B99" s="7" t="inlineStr">
+      <c r="C99" s="7" t="inlineStr">
         <is>
           <t>integer</t>
         </is>
       </c>
-      <c r="C99" s="7" t="inlineStr">
+      <c r="D99" s="7" t="inlineStr">
         <is>
           <t>PK</t>
         </is>
       </c>
-      <c r="D99" s="7" t="inlineStr">
+      <c r="E99" s="7" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="E99" s="7" t="inlineStr">
+      <c r="F99" s="7" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="F99" s="7" t="inlineStr">
+      <c r="G99" s="7" t="inlineStr">
         <is>
           <t>識別號</t>
         </is>
       </c>
-      <c r="G99" s="8" t="inlineStr"/>
+      <c r="H99" s="8" t="inlineStr">
+        <is>
+          <t>識別號</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" s="5" t="inlineStr">
         <is>
+          <t>商品主檔</t>
+        </is>
+      </c>
+      <c r="B100" s="5" t="inlineStr">
+        <is>
           <t>product.template.attribute.line</t>
         </is>
       </c>
-      <c r="B100" s="5" t="inlineStr">
+      <c r="C100" s="5" t="inlineStr">
         <is>
           <t>many2one</t>
         </is>
       </c>
-      <c r="C100" s="5" t="inlineStr">
+      <c r="D100" s="5" t="inlineStr">
         <is>
           <t>FK</t>
         </is>
       </c>
-      <c r="D100" s="5" t="inlineStr">
+      <c r="E100" s="5" t="inlineStr">
         <is>
           <t>product_tmpl_id</t>
         </is>
       </c>
-      <c r="E100" s="5" t="inlineStr">
+      <c r="F100" s="5" t="inlineStr">
         <is>
           <t>Product Template</t>
         </is>
       </c>
-      <c r="F100" s="5" t="inlineStr">
+      <c r="G100" s="5" t="inlineStr">
         <is>
           <t>產品模板</t>
         </is>
       </c>
-      <c r="G100" s="6" t="inlineStr">
-        <is>
-          <t>required cascade</t>
+      <c r="H100" s="6" t="inlineStr">
+        <is>
+          <t>產品模板 · required cascade</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="7" t="inlineStr">
         <is>
+          <t>商品主檔</t>
+        </is>
+      </c>
+      <c r="B101" s="7" t="inlineStr">
+        <is>
           <t>product.template.attribute.line</t>
         </is>
       </c>
-      <c r="B101" s="7" t="inlineStr">
+      <c r="C101" s="7" t="inlineStr">
         <is>
           <t>many2one</t>
         </is>
       </c>
-      <c r="C101" s="7" t="inlineStr">
+      <c r="D101" s="7" t="inlineStr">
         <is>
           <t>FK</t>
         </is>
       </c>
-      <c r="D101" s="7" t="inlineStr">
+      <c r="E101" s="7" t="inlineStr">
         <is>
           <t>attribute_id</t>
         </is>
       </c>
-      <c r="E101" s="7" t="inlineStr">
+      <c r="F101" s="7" t="inlineStr">
         <is>
           <t>Attribute</t>
         </is>
       </c>
-      <c r="F101" s="7" t="inlineStr">
+      <c r="G101" s="7" t="inlineStr">
         <is>
           <t>屬性</t>
         </is>
       </c>
-      <c r="G101" s="8" t="inlineStr">
-        <is>
-          <t>required restrict</t>
+      <c r="H101" s="8" t="inlineStr">
+        <is>
+          <t>屬性 · required restrict</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="5" t="inlineStr">
         <is>
+          <t>商品主檔</t>
+        </is>
+      </c>
+      <c r="B102" s="5" t="inlineStr">
+        <is>
           <t>product.template.attribute.value</t>
         </is>
       </c>
-      <c r="B102" s="5" t="inlineStr">
+      <c r="C102" s="5" t="inlineStr">
         <is>
           <t>integer</t>
         </is>
       </c>
-      <c r="C102" s="5" t="inlineStr">
+      <c r="D102" s="5" t="inlineStr">
         <is>
           <t>PK</t>
         </is>
       </c>
-      <c r="D102" s="5" t="inlineStr">
+      <c r="E102" s="5" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="E102" s="5" t="inlineStr">
+      <c r="F102" s="5" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="F102" s="5" t="inlineStr">
+      <c r="G102" s="5" t="inlineStr">
         <is>
           <t>識別號</t>
         </is>
       </c>
-      <c r="G102" s="6" t="inlineStr"/>
+      <c r="H102" s="6" t="inlineStr">
+        <is>
+          <t>識別號</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" s="7" t="inlineStr">
         <is>
+          <t>商品主檔</t>
+        </is>
+      </c>
+      <c r="B103" s="7" t="inlineStr">
+        <is>
           <t>product.template.attribute.value</t>
         </is>
       </c>
-      <c r="B103" s="7" t="inlineStr">
+      <c r="C103" s="7" t="inlineStr">
         <is>
           <t>many2one</t>
         </is>
       </c>
-      <c r="C103" s="7" t="inlineStr">
+      <c r="D103" s="7" t="inlineStr">
         <is>
           <t>FK</t>
         </is>
       </c>
-      <c r="D103" s="7" t="inlineStr">
+      <c r="E103" s="7" t="inlineStr">
         <is>
           <t>attribute_line_id</t>
         </is>
       </c>
-      <c r="E103" s="7" t="inlineStr">
+      <c r="F103" s="7" t="inlineStr">
         <is>
           <t>Attribute Line</t>
         </is>
       </c>
-      <c r="F103" s="7" t="inlineStr">
+      <c r="G103" s="7" t="inlineStr">
         <is>
           <t>屬性資料行</t>
         </is>
       </c>
-      <c r="G103" s="8" t="inlineStr">
-        <is>
-          <t>required cascade</t>
+      <c r="H103" s="8" t="inlineStr">
+        <is>
+          <t>屬性資料行 · required cascade</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="5" t="inlineStr">
         <is>
+          <t>商品主檔</t>
+        </is>
+      </c>
+      <c r="B104" s="5" t="inlineStr">
+        <is>
           <t>product.template.attribute.value</t>
         </is>
       </c>
-      <c r="B104" s="5" t="inlineStr">
+      <c r="C104" s="5" t="inlineStr">
         <is>
           <t>many2one</t>
         </is>
       </c>
-      <c r="C104" s="5" t="inlineStr">
+      <c r="D104" s="5" t="inlineStr">
         <is>
           <t>FK</t>
         </is>
       </c>
-      <c r="D104" s="5" t="inlineStr">
+      <c r="E104" s="5" t="inlineStr">
         <is>
           <t>product_attribute_value_id</t>
         </is>
       </c>
-      <c r="E104" s="5" t="inlineStr">
+      <c r="F104" s="5" t="inlineStr">
         <is>
           <t>Attribute Value</t>
         </is>
       </c>
-      <c r="F104" s="5" t="inlineStr">
+      <c r="G104" s="5" t="inlineStr">
         <is>
           <t>屬性值</t>
         </is>
       </c>
-      <c r="G104" s="6" t="inlineStr">
-        <is>
-          <t>required cascade</t>
+      <c r="H104" s="6" t="inlineStr">
+        <is>
+          <t>屬性值 · required cascade</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="7" t="inlineStr">
         <is>
+          <t>商品主檔</t>
+        </is>
+      </c>
+      <c r="B105" s="7" t="inlineStr">
+        <is>
           <t>product_variant_combination</t>
         </is>
       </c>
-      <c r="B105" s="7" t="inlineStr">
+      <c r="C105" s="7" t="inlineStr">
         <is>
           <t>integer</t>
         </is>
       </c>
-      <c r="C105" s="7" t="inlineStr">
+      <c r="D105" s="7" t="inlineStr">
         <is>
           <t>PK,FK</t>
         </is>
       </c>
-      <c r="D105" s="7" t="inlineStr">
+      <c r="E105" s="7" t="inlineStr">
         <is>
           <t>product_product_id</t>
         </is>
       </c>
-      <c r="E105" s="7" t="inlineStr">
+      <c r="F105" s="7" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F105" s="7" t="inlineStr">
+      <c r="G105" s="7" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G105" s="8" t="inlineStr">
+      <c r="H105" s="8" t="inlineStr">
         <is>
           <t>中介表欄位，無 model 層標籤；NOT NULL cascade</t>
         </is>
@@ -4288,35 +4926,40 @@
     <row r="106">
       <c r="A106" s="5" t="inlineStr">
         <is>
+          <t>商品主檔</t>
+        </is>
+      </c>
+      <c r="B106" s="5" t="inlineStr">
+        <is>
           <t>product_variant_combination</t>
         </is>
       </c>
-      <c r="B106" s="5" t="inlineStr">
+      <c r="C106" s="5" t="inlineStr">
         <is>
           <t>integer</t>
         </is>
       </c>
-      <c r="C106" s="5" t="inlineStr">
+      <c r="D106" s="5" t="inlineStr">
         <is>
           <t>PK,FK</t>
         </is>
       </c>
-      <c r="D106" s="5" t="inlineStr">
+      <c r="E106" s="5" t="inlineStr">
         <is>
           <t>product_template_attribute_value_id</t>
         </is>
       </c>
-      <c r="E106" s="5" t="inlineStr">
+      <c r="F106" s="5" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F106" s="5" t="inlineStr">
+      <c r="G106" s="5" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G106" s="6" t="inlineStr">
+      <c r="H106" s="6" t="inlineStr">
         <is>
           <t>中介表欄位，無 model 層標籤；NOT NULL restrict</t>
         </is>
@@ -4325,35 +4968,40 @@
     <row r="107">
       <c r="A107" s="7" t="inlineStr">
         <is>
+          <t>商品主檔</t>
+        </is>
+      </c>
+      <c r="B107" s="7" t="inlineStr">
+        <is>
           <t>product_attribute_value_product_template_attribute_line_rel</t>
         </is>
       </c>
-      <c r="B107" s="7" t="inlineStr">
+      <c r="C107" s="7" t="inlineStr">
         <is>
           <t>integer</t>
         </is>
       </c>
-      <c r="C107" s="7" t="inlineStr">
+      <c r="D107" s="7" t="inlineStr">
         <is>
           <t>PK,FK</t>
         </is>
       </c>
-      <c r="D107" s="7" t="inlineStr">
+      <c r="E107" s="7" t="inlineStr">
         <is>
           <t>product_attribute_value_id</t>
         </is>
       </c>
-      <c r="E107" s="7" t="inlineStr">
+      <c r="F107" s="7" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F107" s="7" t="inlineStr">
+      <c r="G107" s="7" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G107" s="8" t="inlineStr">
+      <c r="H107" s="8" t="inlineStr">
         <is>
           <t>中介表欄位，無 model 層標籤；NOT NULL restrict</t>
         </is>
@@ -4362,42 +5010,1233 @@
     <row r="108">
       <c r="A108" s="5" t="inlineStr">
         <is>
+          <t>商品主檔</t>
+        </is>
+      </c>
+      <c r="B108" s="5" t="inlineStr">
+        <is>
           <t>product_attribute_value_product_template_attribute_line_rel</t>
         </is>
       </c>
-      <c r="B108" s="5" t="inlineStr">
+      <c r="C108" s="5" t="inlineStr">
         <is>
           <t>integer</t>
         </is>
       </c>
-      <c r="C108" s="5" t="inlineStr">
+      <c r="D108" s="5" t="inlineStr">
         <is>
           <t>PK,FK</t>
         </is>
       </c>
-      <c r="D108" s="5" t="inlineStr">
+      <c r="E108" s="5" t="inlineStr">
         <is>
           <t>product_template_attribute_line_id</t>
         </is>
       </c>
-      <c r="E108" s="5" t="inlineStr">
+      <c r="F108" s="5" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F108" s="5" t="inlineStr">
+      <c r="G108" s="5" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G108" s="6" t="inlineStr">
+      <c r="H108" s="6" t="inlineStr">
         <is>
           <t>中介表欄位，無 model 層標籤；NOT NULL cascade</t>
         </is>
       </c>
     </row>
+    <row r="109">
+      <c r="A109" s="7" t="inlineStr">
+        <is>
+          <t>採購</t>
+        </is>
+      </c>
+      <c r="B109" s="7" t="inlineStr">
+        <is>
+          <t>purchase.order</t>
+        </is>
+      </c>
+      <c r="C109" s="7" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="D109" s="7" t="inlineStr">
+        <is>
+          <t>PK</t>
+        </is>
+      </c>
+      <c r="E109" s="7" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="F109" s="7" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="G109" s="7" t="inlineStr">
+        <is>
+          <t>識別號</t>
+        </is>
+      </c>
+      <c r="H109" s="8" t="inlineStr">
+        <is>
+          <t>識別號</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="5" t="inlineStr">
+        <is>
+          <t>採購</t>
+        </is>
+      </c>
+      <c r="B110" s="5" t="inlineStr">
+        <is>
+          <t>purchase.order</t>
+        </is>
+      </c>
+      <c r="C110" s="5" t="inlineStr">
+        <is>
+          <t>char</t>
+        </is>
+      </c>
+      <c r="D110" s="5" t="inlineStr"/>
+      <c r="E110" s="5" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="F110" s="5" t="inlineStr">
+        <is>
+          <t>Order Reference</t>
+        </is>
+      </c>
+      <c r="G110" s="5" t="inlineStr">
+        <is>
+          <t>訂單關聯</t>
+        </is>
+      </c>
+      <c r="H110" s="6" t="inlineStr">
+        <is>
+          <t>訂單關聯 · 單號，無 UNIQUE 約束</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="7" t="inlineStr">
+        <is>
+          <t>採購</t>
+        </is>
+      </c>
+      <c r="B111" s="7" t="inlineStr">
+        <is>
+          <t>purchase.order</t>
+        </is>
+      </c>
+      <c r="C111" s="7" t="inlineStr">
+        <is>
+          <t>datetime</t>
+        </is>
+      </c>
+      <c r="D111" s="7" t="inlineStr"/>
+      <c r="E111" s="7" t="inlineStr">
+        <is>
+          <t>date_order</t>
+        </is>
+      </c>
+      <c r="F111" s="7" t="inlineStr">
+        <is>
+          <t>Order Deadline</t>
+        </is>
+      </c>
+      <c r="G111" s="7" t="inlineStr">
+        <is>
+          <t>訂單截止日</t>
+        </is>
+      </c>
+      <c r="H111" s="8" t="inlineStr">
+        <is>
+          <t>訂單截止日 · required</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="5" t="inlineStr">
+        <is>
+          <t>採購</t>
+        </is>
+      </c>
+      <c r="B112" s="5" t="inlineStr">
+        <is>
+          <t>purchase.order</t>
+        </is>
+      </c>
+      <c r="C112" s="5" t="inlineStr">
+        <is>
+          <t>selection</t>
+        </is>
+      </c>
+      <c r="D112" s="5" t="inlineStr"/>
+      <c r="E112" s="5" t="inlineStr">
+        <is>
+          <t>state</t>
+        </is>
+      </c>
+      <c r="F112" s="5" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="G112" s="5" t="inlineStr">
+        <is>
+          <t>狀態</t>
+        </is>
+      </c>
+      <c r="H112" s="6" t="inlineStr">
+        <is>
+          <t>狀態 · draft / sent / to approve / purchase / cancel</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="7" t="inlineStr">
+        <is>
+          <t>採購</t>
+        </is>
+      </c>
+      <c r="B113" s="7" t="inlineStr">
+        <is>
+          <t>purchase.order</t>
+        </is>
+      </c>
+      <c r="C113" s="7" t="inlineStr">
+        <is>
+          <t>many2one</t>
+        </is>
+      </c>
+      <c r="D113" s="7" t="inlineStr">
+        <is>
+          <t>FK</t>
+        </is>
+      </c>
+      <c r="E113" s="7" t="inlineStr">
+        <is>
+          <t>partner_id</t>
+        </is>
+      </c>
+      <c r="F113" s="7" t="inlineStr">
+        <is>
+          <t>Vendor</t>
+        </is>
+      </c>
+      <c r="G113" s="7" t="inlineStr">
+        <is>
+          <t>供應商</t>
+        </is>
+      </c>
+      <c r="H113" s="8" t="inlineStr">
+        <is>
+          <t>供應商 · required restrict</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="5" t="inlineStr">
+        <is>
+          <t>採購</t>
+        </is>
+      </c>
+      <c r="B114" s="5" t="inlineStr">
+        <is>
+          <t>purchase.order</t>
+        </is>
+      </c>
+      <c r="C114" s="5" t="inlineStr">
+        <is>
+          <t>many2one</t>
+        </is>
+      </c>
+      <c r="D114" s="5" t="inlineStr">
+        <is>
+          <t>FK</t>
+        </is>
+      </c>
+      <c r="E114" s="5" t="inlineStr">
+        <is>
+          <t>company_id</t>
+        </is>
+      </c>
+      <c r="F114" s="5" t="inlineStr">
+        <is>
+          <t>Company</t>
+        </is>
+      </c>
+      <c r="G114" s="5" t="inlineStr">
+        <is>
+          <t>公司</t>
+        </is>
+      </c>
+      <c r="H114" s="6" t="inlineStr">
+        <is>
+          <t>公司 · required restrict</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="7" t="inlineStr">
+        <is>
+          <t>採購</t>
+        </is>
+      </c>
+      <c r="B115" s="7" t="inlineStr">
+        <is>
+          <t>purchase.order</t>
+        </is>
+      </c>
+      <c r="C115" s="7" t="inlineStr">
+        <is>
+          <t>many2one</t>
+        </is>
+      </c>
+      <c r="D115" s="7" t="inlineStr">
+        <is>
+          <t>FK</t>
+        </is>
+      </c>
+      <c r="E115" s="7" t="inlineStr">
+        <is>
+          <t>currency_id</t>
+        </is>
+      </c>
+      <c r="F115" s="7" t="inlineStr">
+        <is>
+          <t>Currency</t>
+        </is>
+      </c>
+      <c r="G115" s="7" t="inlineStr">
+        <is>
+          <t>貨幣</t>
+        </is>
+      </c>
+      <c r="H115" s="8" t="inlineStr">
+        <is>
+          <t>貨幣 · required restrict 圖外</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="5" t="inlineStr">
+        <is>
+          <t>採購</t>
+        </is>
+      </c>
+      <c r="B116" s="5" t="inlineStr">
+        <is>
+          <t>purchase.order</t>
+        </is>
+      </c>
+      <c r="C116" s="5" t="inlineStr">
+        <is>
+          <t>many2one</t>
+        </is>
+      </c>
+      <c r="D116" s="5" t="inlineStr">
+        <is>
+          <t>FK</t>
+        </is>
+      </c>
+      <c r="E116" s="5" t="inlineStr">
+        <is>
+          <t>picking_type_id</t>
+        </is>
+      </c>
+      <c r="F116" s="5" t="inlineStr">
+        <is>
+          <t>Deliver To</t>
+        </is>
+      </c>
+      <c r="G116" s="5" t="inlineStr">
+        <is>
+          <t>交貨到</t>
+        </is>
+      </c>
+      <c r="H116" s="6" t="inlineStr">
+        <is>
+          <t>交貨到 · required restrict 圖外</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="7" t="inlineStr">
+        <is>
+          <t>採購</t>
+        </is>
+      </c>
+      <c r="B117" s="7" t="inlineStr">
+        <is>
+          <t>purchase.order</t>
+        </is>
+      </c>
+      <c r="C117" s="7" t="inlineStr">
+        <is>
+          <t>many2one</t>
+        </is>
+      </c>
+      <c r="D117" s="7" t="inlineStr">
+        <is>
+          <t>FK</t>
+        </is>
+      </c>
+      <c r="E117" s="7" t="inlineStr">
+        <is>
+          <t>dest_address_id</t>
+        </is>
+      </c>
+      <c r="F117" s="7" t="inlineStr">
+        <is>
+          <t>Dropship Address</t>
+        </is>
+      </c>
+      <c r="G117" s="7" t="inlineStr">
+        <is>
+          <t>直運地址</t>
+        </is>
+      </c>
+      <c r="H117" s="8" t="inlineStr">
+        <is>
+          <t>直運地址 · 選填 set-null</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="5" t="inlineStr">
+        <is>
+          <t>採購</t>
+        </is>
+      </c>
+      <c r="B118" s="5" t="inlineStr">
+        <is>
+          <t>purchase.order</t>
+        </is>
+      </c>
+      <c r="C118" s="5" t="inlineStr">
+        <is>
+          <t>many2one</t>
+        </is>
+      </c>
+      <c r="D118" s="5" t="inlineStr">
+        <is>
+          <t>FK</t>
+        </is>
+      </c>
+      <c r="E118" s="5" t="inlineStr">
+        <is>
+          <t>payment_term_id</t>
+        </is>
+      </c>
+      <c r="F118" s="5" t="inlineStr">
+        <is>
+          <t>Payment Terms</t>
+        </is>
+      </c>
+      <c r="G118" s="5" t="inlineStr">
+        <is>
+          <t>付款條件</t>
+        </is>
+      </c>
+      <c r="H118" s="6" t="inlineStr">
+        <is>
+          <t>付款條件 · 選填 set-null</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="7" t="inlineStr">
+        <is>
+          <t>採購</t>
+        </is>
+      </c>
+      <c r="B119" s="7" t="inlineStr">
+        <is>
+          <t>purchase.order</t>
+        </is>
+      </c>
+      <c r="C119" s="7" t="inlineStr">
+        <is>
+          <t>many2one</t>
+        </is>
+      </c>
+      <c r="D119" s="7" t="inlineStr">
+        <is>
+          <t>FK</t>
+        </is>
+      </c>
+      <c r="E119" s="7" t="inlineStr">
+        <is>
+          <t>user_id</t>
+        </is>
+      </c>
+      <c r="F119" s="7" t="inlineStr">
+        <is>
+          <t>Buyer</t>
+        </is>
+      </c>
+      <c r="G119" s="7" t="inlineStr">
+        <is>
+          <t>買方</t>
+        </is>
+      </c>
+      <c r="H119" s="8" t="inlineStr">
+        <is>
+          <t>買方 · 選填 set-null</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="5" t="inlineStr">
+        <is>
+          <t>採購</t>
+        </is>
+      </c>
+      <c r="B120" s="5" t="inlineStr">
+        <is>
+          <t>purchase.order</t>
+        </is>
+      </c>
+      <c r="C120" s="5" t="inlineStr">
+        <is>
+          <t>many2one</t>
+        </is>
+      </c>
+      <c r="D120" s="5" t="inlineStr">
+        <is>
+          <t>FK</t>
+        </is>
+      </c>
+      <c r="E120" s="5" t="inlineStr">
+        <is>
+          <t>fiscal_position_id</t>
+        </is>
+      </c>
+      <c r="F120" s="5" t="inlineStr">
+        <is>
+          <t>Fiscal Position</t>
+        </is>
+      </c>
+      <c r="G120" s="5" t="inlineStr">
+        <is>
+          <t>財務規則</t>
+        </is>
+      </c>
+      <c r="H120" s="6" t="inlineStr">
+        <is>
+          <t>財務規則 · 選填 圖外</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="7" t="inlineStr">
+        <is>
+          <t>採購</t>
+        </is>
+      </c>
+      <c r="B121" s="7" t="inlineStr">
+        <is>
+          <t>purchase.order</t>
+        </is>
+      </c>
+      <c r="C121" s="7" t="inlineStr">
+        <is>
+          <t>many2one</t>
+        </is>
+      </c>
+      <c r="D121" s="7" t="inlineStr">
+        <is>
+          <t>FK</t>
+        </is>
+      </c>
+      <c r="E121" s="7" t="inlineStr">
+        <is>
+          <t>incoterm_id</t>
+        </is>
+      </c>
+      <c r="F121" s="7" t="inlineStr">
+        <is>
+          <t>Incoterm</t>
+        </is>
+      </c>
+      <c r="G121" s="7" t="inlineStr">
+        <is>
+          <t>國際貿易術語</t>
+        </is>
+      </c>
+      <c r="H121" s="8" t="inlineStr">
+        <is>
+          <t>國際貿易術語 · 選填 圖外</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="5" t="inlineStr">
+        <is>
+          <t>採購</t>
+        </is>
+      </c>
+      <c r="B122" s="5" t="inlineStr">
+        <is>
+          <t>purchase.order.line</t>
+        </is>
+      </c>
+      <c r="C122" s="5" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="D122" s="5" t="inlineStr">
+        <is>
+          <t>PK</t>
+        </is>
+      </c>
+      <c r="E122" s="5" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="F122" s="5" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="G122" s="5" t="inlineStr">
+        <is>
+          <t>識別號</t>
+        </is>
+      </c>
+      <c r="H122" s="6" t="inlineStr">
+        <is>
+          <t>識別號</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="7" t="inlineStr">
+        <is>
+          <t>採購</t>
+        </is>
+      </c>
+      <c r="B123" s="7" t="inlineStr">
+        <is>
+          <t>purchase.order.line</t>
+        </is>
+      </c>
+      <c r="C123" s="7" t="inlineStr">
+        <is>
+          <t>many2one</t>
+        </is>
+      </c>
+      <c r="D123" s="7" t="inlineStr">
+        <is>
+          <t>FK</t>
+        </is>
+      </c>
+      <c r="E123" s="7" t="inlineStr">
+        <is>
+          <t>order_id</t>
+        </is>
+      </c>
+      <c r="F123" s="7" t="inlineStr">
+        <is>
+          <t>Order Reference</t>
+        </is>
+      </c>
+      <c r="G123" s="7" t="inlineStr">
+        <is>
+          <t>訂單關聯</t>
+        </is>
+      </c>
+      <c r="H123" s="8" t="inlineStr">
+        <is>
+          <t>訂單關聯 · required cascade</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="5" t="inlineStr">
+        <is>
+          <t>採購</t>
+        </is>
+      </c>
+      <c r="B124" s="5" t="inlineStr">
+        <is>
+          <t>purchase.order.line</t>
+        </is>
+      </c>
+      <c r="C124" s="5" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="D124" s="5" t="inlineStr"/>
+      <c r="E124" s="5" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="F124" s="5" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="G124" s="5" t="inlineStr">
+        <is>
+          <t>說明</t>
+        </is>
+      </c>
+      <c r="H124" s="6" t="inlineStr">
+        <is>
+          <t>說明 · required</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="7" t="inlineStr">
+        <is>
+          <t>採購</t>
+        </is>
+      </c>
+      <c r="B125" s="7" t="inlineStr">
+        <is>
+          <t>purchase.order.line</t>
+        </is>
+      </c>
+      <c r="C125" s="7" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="D125" s="7" t="inlineStr"/>
+      <c r="E125" s="7" t="inlineStr">
+        <is>
+          <t>product_qty</t>
+        </is>
+      </c>
+      <c r="F125" s="7" t="inlineStr">
+        <is>
+          <t>Quantity</t>
+        </is>
+      </c>
+      <c r="G125" s="7" t="inlineStr">
+        <is>
+          <t>數量</t>
+        </is>
+      </c>
+      <c r="H125" s="8" t="inlineStr">
+        <is>
+          <t>數量 · required</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="5" t="inlineStr">
+        <is>
+          <t>採購</t>
+        </is>
+      </c>
+      <c r="B126" s="5" t="inlineStr">
+        <is>
+          <t>purchase.order.line</t>
+        </is>
+      </c>
+      <c r="C126" s="5" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="D126" s="5" t="inlineStr"/>
+      <c r="E126" s="5" t="inlineStr">
+        <is>
+          <t>price_unit</t>
+        </is>
+      </c>
+      <c r="F126" s="5" t="inlineStr">
+        <is>
+          <t>Unit Price</t>
+        </is>
+      </c>
+      <c r="G126" s="5" t="inlineStr">
+        <is>
+          <t>單價</t>
+        </is>
+      </c>
+      <c r="H126" s="6" t="inlineStr">
+        <is>
+          <t>單價 · required</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="7" t="inlineStr">
+        <is>
+          <t>採購</t>
+        </is>
+      </c>
+      <c r="B127" s="7" t="inlineStr">
+        <is>
+          <t>purchase.order.line</t>
+        </is>
+      </c>
+      <c r="C127" s="7" t="inlineStr">
+        <is>
+          <t>selection</t>
+        </is>
+      </c>
+      <c r="D127" s="7" t="inlineStr"/>
+      <c r="E127" s="7" t="inlineStr">
+        <is>
+          <t>display_type</t>
+        </is>
+      </c>
+      <c r="F127" s="7" t="inlineStr">
+        <is>
+          <t>Display Type</t>
+        </is>
+      </c>
+      <c r="G127" s="7" t="inlineStr">
+        <is>
+          <t>顯示類型</t>
+        </is>
+      </c>
+      <c r="H127" s="8" t="inlineStr">
+        <is>
+          <t>顯示類型 · 決定下三欄必填與否</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="5" t="inlineStr">
+        <is>
+          <t>採購</t>
+        </is>
+      </c>
+      <c r="B128" s="5" t="inlineStr">
+        <is>
+          <t>purchase.order.line</t>
+        </is>
+      </c>
+      <c r="C128" s="5" t="inlineStr">
+        <is>
+          <t>many2one</t>
+        </is>
+      </c>
+      <c r="D128" s="5" t="inlineStr">
+        <is>
+          <t>FK</t>
+        </is>
+      </c>
+      <c r="E128" s="5" t="inlineStr">
+        <is>
+          <t>product_id</t>
+        </is>
+      </c>
+      <c r="F128" s="5" t="inlineStr">
+        <is>
+          <t>Product</t>
+        </is>
+      </c>
+      <c r="G128" s="5" t="inlineStr">
+        <is>
+          <t>商品</t>
+        </is>
+      </c>
+      <c r="H128" s="6" t="inlineStr">
+        <is>
+          <t>商品 · CHECK 條件式必填 restrict</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="7" t="inlineStr">
+        <is>
+          <t>採購</t>
+        </is>
+      </c>
+      <c r="B129" s="7" t="inlineStr">
+        <is>
+          <t>purchase.order.line</t>
+        </is>
+      </c>
+      <c r="C129" s="7" t="inlineStr">
+        <is>
+          <t>many2one</t>
+        </is>
+      </c>
+      <c r="D129" s="7" t="inlineStr">
+        <is>
+          <t>FK</t>
+        </is>
+      </c>
+      <c r="E129" s="7" t="inlineStr">
+        <is>
+          <t>product_uom_id</t>
+        </is>
+      </c>
+      <c r="F129" s="7" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="G129" s="7" t="inlineStr">
+        <is>
+          <t>單位</t>
+        </is>
+      </c>
+      <c r="H129" s="8" t="inlineStr">
+        <is>
+          <t>單位 · CHECK 條件式必填 restrict</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="5" t="inlineStr">
+        <is>
+          <t>採購</t>
+        </is>
+      </c>
+      <c r="B130" s="5" t="inlineStr">
+        <is>
+          <t>purchase.order.line</t>
+        </is>
+      </c>
+      <c r="C130" s="5" t="inlineStr">
+        <is>
+          <t>datetime</t>
+        </is>
+      </c>
+      <c r="D130" s="5" t="inlineStr"/>
+      <c r="E130" s="5" t="inlineStr">
+        <is>
+          <t>date_planned</t>
+        </is>
+      </c>
+      <c r="F130" s="5" t="inlineStr">
+        <is>
+          <t>Expected Arrival</t>
+        </is>
+      </c>
+      <c r="G130" s="5" t="inlineStr">
+        <is>
+          <t>預計到貨</t>
+        </is>
+      </c>
+      <c r="H130" s="6" t="inlineStr">
+        <is>
+          <t>預計到貨 · CHECK 條件式必填</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="7" t="inlineStr">
+        <is>
+          <t>採購</t>
+        </is>
+      </c>
+      <c r="B131" s="7" t="inlineStr">
+        <is>
+          <t>purchase.order.line</t>
+        </is>
+      </c>
+      <c r="C131" s="7" t="inlineStr">
+        <is>
+          <t>many2one</t>
+        </is>
+      </c>
+      <c r="D131" s="7" t="inlineStr">
+        <is>
+          <t>FK</t>
+        </is>
+      </c>
+      <c r="E131" s="7" t="inlineStr">
+        <is>
+          <t>partner_id</t>
+        </is>
+      </c>
+      <c r="F131" s="7" t="inlineStr">
+        <is>
+          <t>Partner</t>
+        </is>
+      </c>
+      <c r="G131" s="7" t="inlineStr">
+        <is>
+          <t>業務夥伴</t>
+        </is>
+      </c>
+      <c r="H131" s="8" t="inlineStr">
+        <is>
+          <t>業務夥伴 · 選填</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="5" t="inlineStr">
+        <is>
+          <t>採購</t>
+        </is>
+      </c>
+      <c r="B132" s="5" t="inlineStr">
+        <is>
+          <t>purchase.order.line</t>
+        </is>
+      </c>
+      <c r="C132" s="5" t="inlineStr">
+        <is>
+          <t>many2one</t>
+        </is>
+      </c>
+      <c r="D132" s="5" t="inlineStr">
+        <is>
+          <t>FK</t>
+        </is>
+      </c>
+      <c r="E132" s="5" t="inlineStr">
+        <is>
+          <t>company_id</t>
+        </is>
+      </c>
+      <c r="F132" s="5" t="inlineStr">
+        <is>
+          <t>Company</t>
+        </is>
+      </c>
+      <c r="G132" s="5" t="inlineStr">
+        <is>
+          <t>公司</t>
+        </is>
+      </c>
+      <c r="H132" s="6" t="inlineStr">
+        <is>
+          <t>公司 · 選填</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="7" t="inlineStr">
+        <is>
+          <t>採購</t>
+        </is>
+      </c>
+      <c r="B133" s="7" t="inlineStr">
+        <is>
+          <t>purchase.order.line</t>
+        </is>
+      </c>
+      <c r="C133" s="7" t="inlineStr">
+        <is>
+          <t>many2one</t>
+        </is>
+      </c>
+      <c r="D133" s="7" t="inlineStr">
+        <is>
+          <t>FK</t>
+        </is>
+      </c>
+      <c r="E133" s="7" t="inlineStr">
+        <is>
+          <t>location_final_id</t>
+        </is>
+      </c>
+      <c r="F133" s="7" t="inlineStr">
+        <is>
+          <t>Location from procurement</t>
+        </is>
+      </c>
+      <c r="G133" s="7" t="inlineStr">
+        <is>
+          <t>採購物資位置</t>
+        </is>
+      </c>
+      <c r="H133" s="8" t="inlineStr">
+        <is>
+          <t>採購物資位置 · 選填 圖外</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="5" t="inlineStr">
+        <is>
+          <t>採購</t>
+        </is>
+      </c>
+      <c r="B134" s="5" t="inlineStr">
+        <is>
+          <t>purchase.order.line</t>
+        </is>
+      </c>
+      <c r="C134" s="5" t="inlineStr">
+        <is>
+          <t>many2one</t>
+        </is>
+      </c>
+      <c r="D134" s="5" t="inlineStr">
+        <is>
+          <t>FK</t>
+        </is>
+      </c>
+      <c r="E134" s="5" t="inlineStr">
+        <is>
+          <t>orderpoint_id</t>
+        </is>
+      </c>
+      <c r="F134" s="5" t="inlineStr">
+        <is>
+          <t>Orderpoint</t>
+        </is>
+      </c>
+      <c r="G134" s="5" t="inlineStr">
+        <is>
+          <t>訂貨點</t>
+        </is>
+      </c>
+      <c r="H134" s="6" t="inlineStr">
+        <is>
+          <t>訂貨點 · 選填 圖外</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="7" t="inlineStr">
+        <is>
+          <t>採購</t>
+        </is>
+      </c>
+      <c r="B135" s="7" t="inlineStr">
+        <is>
+          <t>purchase.order.line</t>
+        </is>
+      </c>
+      <c r="C135" s="7" t="inlineStr">
+        <is>
+          <t>many2one</t>
+        </is>
+      </c>
+      <c r="D135" s="7" t="inlineStr">
+        <is>
+          <t>FK</t>
+        </is>
+      </c>
+      <c r="E135" s="7" t="inlineStr">
+        <is>
+          <t>sale_line_id</t>
+        </is>
+      </c>
+      <c r="F135" s="7" t="inlineStr">
+        <is>
+          <t>Origin Sale Item</t>
+        </is>
+      </c>
+      <c r="G135" s="7" t="inlineStr">
+        <is>
+          <t>原始銷售項目</t>
+        </is>
+      </c>
+      <c r="H135" s="8" t="inlineStr">
+        <is>
+          <t>原始銷售項目 · 選填 圖外</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="5" t="inlineStr">
+        <is>
+          <t>採購</t>
+        </is>
+      </c>
+      <c r="B136" s="5" t="inlineStr">
+        <is>
+          <t>product_template_attribute_value_purchase_order_line_rel</t>
+        </is>
+      </c>
+      <c r="C136" s="5" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="D136" s="5" t="inlineStr">
+        <is>
+          <t>PK,FK</t>
+        </is>
+      </c>
+      <c r="E136" s="5" t="inlineStr">
+        <is>
+          <t>purchase_order_line_id</t>
+        </is>
+      </c>
+      <c r="F136" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G136" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H136" s="6" t="inlineStr">
+        <is>
+          <t>中介表欄位，無 model 層標籤；NOT NULL cascade</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="7" t="inlineStr">
+        <is>
+          <t>採購</t>
+        </is>
+      </c>
+      <c r="B137" s="7" t="inlineStr">
+        <is>
+          <t>product_template_attribute_value_purchase_order_line_rel</t>
+        </is>
+      </c>
+      <c r="C137" s="7" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="D137" s="7" t="inlineStr">
+        <is>
+          <t>PK,FK</t>
+        </is>
+      </c>
+      <c r="E137" s="7" t="inlineStr">
+        <is>
+          <t>product_template_attribute_value_id</t>
+        </is>
+      </c>
+      <c r="F137" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G137" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H137" s="8" t="inlineStr">
+        <is>
+          <t>中介表欄位，無 model 層標籤；NOT NULL restrict</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G108"/>
+  <autoFilter ref="A1:H137"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -4408,32 +6247,38 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D25"/>
+  <dimension ref="A1:E28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="46" customWidth="1" min="1" max="1"/>
-    <col width="40" customWidth="1" min="2" max="2"/>
-    <col width="26" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="46" customWidth="1" min="2" max="2"/>
+    <col width="40" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
+          <t>視圖</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
           <t>實體 (model)</t>
         </is>
       </c>
-      <c r="B1" s="4" t="inlineStr">
+      <c r="C1" s="4" t="inlineStr">
         <is>
           <t>英文</t>
         </is>
       </c>
-      <c r="C1" s="4" t="inlineStr">
+      <c r="D1" s="4" t="inlineStr">
         <is>
           <t>繁體中文</t>
         </is>
       </c>
-      <c r="D1" s="4" t="inlineStr">
+      <c r="E1" s="4" t="inlineStr">
         <is>
           <t>圖上欄位數</t>
         </is>
@@ -4442,485 +6287,680 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
+          <t>聯絡人</t>
+        </is>
+      </c>
+      <c r="B2" s="5" t="inlineStr">
+        <is>
           <t>account.account</t>
         </is>
       </c>
-      <c r="B2" s="5" t="inlineStr">
+      <c r="C2" s="5" t="inlineStr">
         <is>
           <t>Account</t>
         </is>
       </c>
-      <c r="C2" s="5" t="inlineStr">
+      <c r="D2" s="5" t="inlineStr">
         <is>
           <t>帳戶</t>
         </is>
       </c>
-      <c r="D2" s="5" t="n">
+      <c r="E2" s="5" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="7" t="inlineStr">
         <is>
+          <t>聯絡人</t>
+        </is>
+      </c>
+      <c r="B3" s="7" t="inlineStr">
+        <is>
           <t>account.payment.term</t>
         </is>
       </c>
-      <c r="B3" s="7" t="inlineStr">
+      <c r="C3" s="7" t="inlineStr">
         <is>
           <t>Payment Terms</t>
         </is>
       </c>
-      <c r="C3" s="7" t="inlineStr">
+      <c r="D3" s="7" t="inlineStr">
         <is>
           <t>付款條件</t>
         </is>
       </c>
-      <c r="D3" s="7" t="n">
+      <c r="E3" s="7" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>product.attribute</t>
+          <t>聯絡人</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>Product Attribute</t>
+          <t>res.city</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>產品屬性</t>
-        </is>
-      </c>
-      <c r="D4" s="5" t="n">
+          <t>City</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="inlineStr">
+        <is>
+          <t>城市</t>
+        </is>
+      </c>
+      <c r="E4" s="5" t="n">
         <v>4</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="7" t="inlineStr">
         <is>
-          <t>product.attribute.value</t>
+          <t>聯絡人</t>
         </is>
       </c>
       <c r="B5" s="7" t="inlineStr">
         <is>
-          <t>Attribute Value</t>
+          <t>res.company</t>
         </is>
       </c>
       <c r="C5" s="7" t="inlineStr">
         <is>
-          <t>屬性值</t>
-        </is>
-      </c>
-      <c r="D5" s="7" t="n">
-        <v>3</v>
+          <t>Companies</t>
+        </is>
+      </c>
+      <c r="D5" s="7" t="inlineStr">
+        <is>
+          <t>公司</t>
+        </is>
+      </c>
+      <c r="E5" s="7" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>product.category</t>
+          <t>聯絡人</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>Product Category</t>
+          <t>res.country</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>產品分類</t>
-        </is>
-      </c>
-      <c r="D6" s="5" t="n">
+          <t>Country</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>國家 / 地區</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="7" t="inlineStr">
         <is>
-          <t>product.product</t>
+          <t>聯絡人</t>
         </is>
       </c>
       <c r="B7" s="7" t="inlineStr">
         <is>
-          <t>Product Variant</t>
+          <t>res.country.state</t>
         </is>
       </c>
       <c r="C7" s="7" t="inlineStr">
         <is>
-          <t>產品款式</t>
-        </is>
-      </c>
-      <c r="D7" s="7" t="n">
-        <v>2</v>
+          <t>Country state</t>
+        </is>
+      </c>
+      <c r="D7" s="7" t="inlineStr">
+        <is>
+          <t>國家州/省</t>
+        </is>
+      </c>
+      <c r="E7" s="7" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>product.supplierinfo</t>
+          <t>聯絡人</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>Supplier Pricelist</t>
+          <t>res.partner</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>供應商價目表</t>
-        </is>
-      </c>
-      <c r="D8" s="5" t="n">
-        <v>8</v>
+          <t>Contact</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>聯絡人</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>27</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="7" t="inlineStr">
         <is>
-          <t>product.template</t>
+          <t>聯絡人</t>
         </is>
       </c>
       <c r="B9" s="7" t="inlineStr">
         <is>
-          <t>Product</t>
+          <t>res.partner.bank</t>
         </is>
       </c>
       <c r="C9" s="7" t="inlineStr">
         <is>
-          <t>商品</t>
-        </is>
-      </c>
-      <c r="D9" s="7" t="n">
-        <v>8</v>
+          <t>Bank Accounts</t>
+        </is>
+      </c>
+      <c r="D9" s="7" t="inlineStr">
+        <is>
+          <t>銀行帳戶</t>
+        </is>
+      </c>
+      <c r="E9" s="7" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>product.template.attribute.line</t>
+          <t>聯絡人</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>Product Template Attribute Line</t>
+          <t>res.partner.category</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>產品範本屬性資料行</t>
-        </is>
-      </c>
-      <c r="D10" s="5" t="n">
+          <t>Partner Tags</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>合作夥伴標籤</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="7" t="inlineStr">
         <is>
-          <t>product.template.attribute.value</t>
+          <t>聯絡人</t>
         </is>
       </c>
       <c r="B11" s="7" t="inlineStr">
         <is>
-          <t>Product Template Attribute Value</t>
+          <t>res.partner.industry</t>
         </is>
       </c>
       <c r="C11" s="7" t="inlineStr">
         <is>
-          <t>產品模板屬性值</t>
-        </is>
-      </c>
-      <c r="D11" s="7" t="n">
-        <v>3</v>
+          <t>Industry</t>
+        </is>
+      </c>
+      <c r="D11" s="7" t="inlineStr">
+        <is>
+          <t>行業</t>
+        </is>
+      </c>
+      <c r="E11" s="7" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>product.uom</t>
+          <t>聯絡人</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>Link between products and their UoMs</t>
+          <t>res.users</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>連結產品與所使用的計量單位</t>
-        </is>
-      </c>
-      <c r="D12" s="5" t="n">
-        <v>4</v>
+          <t>User</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>使用者</t>
+        </is>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="7" t="inlineStr">
         <is>
-          <t>product_attribute_value_product_template_attribute_line_rel</t>
+          <t>聯絡人</t>
         </is>
       </c>
       <c r="B13" s="7" t="inlineStr">
         <is>
+          <t>res_partner_res_partner_category_rel</t>
+        </is>
+      </c>
+      <c r="C13" s="7" t="inlineStr">
+        <is>
           <t>（中介表，非 model）</t>
         </is>
       </c>
-      <c r="C13" s="7" t="inlineStr">
+      <c r="D13" s="7" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D13" s="7" t="n">
+      <c r="E13" s="7" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>product_variant_combination</t>
+          <t>商品主檔</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>（中介表，非 model）</t>
+          <t>product.attribute</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D14" s="5" t="n">
-        <v>2</v>
+          <t>Product Attribute</t>
+        </is>
+      </c>
+      <c r="D14" s="5" t="inlineStr">
+        <is>
+          <t>產品屬性</t>
+        </is>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="7" t="inlineStr">
         <is>
-          <t>res.city</t>
+          <t>商品主檔</t>
         </is>
       </c>
       <c r="B15" s="7" t="inlineStr">
         <is>
-          <t>City</t>
+          <t>product.attribute.value</t>
         </is>
       </c>
       <c r="C15" s="7" t="inlineStr">
         <is>
-          <t>城市</t>
-        </is>
-      </c>
-      <c r="D15" s="7" t="n">
-        <v>4</v>
+          <t>Attribute Value</t>
+        </is>
+      </c>
+      <c r="D15" s="7" t="inlineStr">
+        <is>
+          <t>屬性值</t>
+        </is>
+      </c>
+      <c r="E15" s="7" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>res.company</t>
+          <t>商品主檔</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>Companies</t>
+          <t>product.category</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>公司</t>
-        </is>
-      </c>
-      <c r="D16" s="5" t="n">
-        <v>2</v>
+          <t>Product Category</t>
+        </is>
+      </c>
+      <c r="D16" s="5" t="inlineStr">
+        <is>
+          <t>產品分類</t>
+        </is>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="7" t="inlineStr">
         <is>
-          <t>res.country</t>
+          <t>商品主檔</t>
         </is>
       </c>
       <c r="B17" s="7" t="inlineStr">
         <is>
-          <t>Country</t>
+          <t>product.product</t>
         </is>
       </c>
       <c r="C17" s="7" t="inlineStr">
         <is>
-          <t>國家 / 地區</t>
-        </is>
-      </c>
-      <c r="D17" s="7" t="n">
-        <v>3</v>
+          <t>Product Variant</t>
+        </is>
+      </c>
+      <c r="D17" s="7" t="inlineStr">
+        <is>
+          <t>產品款式</t>
+        </is>
+      </c>
+      <c r="E17" s="7" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>res.country.state</t>
+          <t>商品主檔</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>Country state</t>
+          <t>product.supplierinfo</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>國家州/省</t>
-        </is>
-      </c>
-      <c r="D18" s="5" t="n">
-        <v>4</v>
+          <t>Supplier Pricelist</t>
+        </is>
+      </c>
+      <c r="D18" s="5" t="inlineStr">
+        <is>
+          <t>供應商價目表</t>
+        </is>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>8</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="7" t="inlineStr">
         <is>
-          <t>res.partner</t>
+          <t>商品主檔</t>
         </is>
       </c>
       <c r="B19" s="7" t="inlineStr">
         <is>
-          <t>Contact</t>
+          <t>product.template</t>
         </is>
       </c>
       <c r="C19" s="7" t="inlineStr">
         <is>
-          <t>聯絡人</t>
-        </is>
-      </c>
-      <c r="D19" s="7" t="n">
-        <v>27</v>
+          <t>Product</t>
+        </is>
+      </c>
+      <c r="D19" s="7" t="inlineStr">
+        <is>
+          <t>商品</t>
+        </is>
+      </c>
+      <c r="E19" s="7" t="n">
+        <v>8</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>res.partner.bank</t>
+          <t>商品主檔</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>Bank Accounts</t>
+          <t>product.template.attribute.line</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>銀行帳戶</t>
-        </is>
-      </c>
-      <c r="D20" s="5" t="n">
-        <v>4</v>
+          <t>Product Template Attribute Line</t>
+        </is>
+      </c>
+      <c r="D20" s="5" t="inlineStr">
+        <is>
+          <t>產品範本屬性資料行</t>
+        </is>
+      </c>
+      <c r="E20" s="5" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="7" t="inlineStr">
         <is>
-          <t>res.partner.category</t>
+          <t>商品主檔</t>
         </is>
       </c>
       <c r="B21" s="7" t="inlineStr">
         <is>
-          <t>Partner Tags</t>
+          <t>product.template.attribute.value</t>
         </is>
       </c>
       <c r="C21" s="7" t="inlineStr">
         <is>
-          <t>合作夥伴標籤</t>
-        </is>
-      </c>
-      <c r="D21" s="7" t="n">
+          <t>Product Template Attribute Value</t>
+        </is>
+      </c>
+      <c r="D21" s="7" t="inlineStr">
+        <is>
+          <t>產品模板屬性值</t>
+        </is>
+      </c>
+      <c r="E21" s="7" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>res.partner.industry</t>
+          <t>商品主檔</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>Industry</t>
+          <t>product.uom</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>行業</t>
-        </is>
-      </c>
-      <c r="D22" s="5" t="n">
-        <v>2</v>
+          <t>Link between products and their UoMs</t>
+        </is>
+      </c>
+      <c r="D22" s="5" t="inlineStr">
+        <is>
+          <t>連結產品與所使用的計量單位</t>
+        </is>
+      </c>
+      <c r="E22" s="5" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="7" t="inlineStr">
         <is>
-          <t>res.users</t>
+          <t>商品主檔</t>
         </is>
       </c>
       <c r="B23" s="7" t="inlineStr">
         <is>
-          <t>User</t>
+          <t>product_attribute_value_product_template_attribute_line_rel</t>
         </is>
       </c>
       <c r="C23" s="7" t="inlineStr">
         <is>
-          <t>使用者</t>
-        </is>
-      </c>
-      <c r="D23" s="7" t="n">
+          <t>（中介表，非 model）</t>
+        </is>
+      </c>
+      <c r="D23" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E23" s="7" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>res_partner_res_partner_category_rel</t>
+          <t>商品主檔</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
+          <t>product_variant_combination</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
           <t>（中介表，非 model）</t>
         </is>
       </c>
-      <c r="C24" s="5" t="inlineStr">
+      <c r="D24" s="5" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D24" s="5" t="n">
+      <c r="E24" s="5" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="7" t="inlineStr">
         <is>
+          <t>商品主檔</t>
+        </is>
+      </c>
+      <c r="B25" s="7" t="inlineStr">
+        <is>
           <t>uom.uom</t>
         </is>
       </c>
-      <c r="B25" s="7" t="inlineStr">
+      <c r="C25" s="7" t="inlineStr">
         <is>
           <t>Product Unit of Measure</t>
         </is>
       </c>
-      <c r="C25" s="7" t="inlineStr">
+      <c r="D25" s="7" t="inlineStr">
         <is>
           <t>產品計量單位</t>
         </is>
       </c>
-      <c r="D25" s="7" t="n">
+      <c r="E25" s="7" t="n">
         <v>6</v>
       </c>
     </row>
+    <row r="26">
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t>採購</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t>product_template_attribute_value_purchase_order_line_rel</t>
+        </is>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>（中介表，非 model）</t>
+        </is>
+      </c>
+      <c r="D26" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E26" s="5" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="7" t="inlineStr">
+        <is>
+          <t>採購</t>
+        </is>
+      </c>
+      <c r="B27" s="7" t="inlineStr">
+        <is>
+          <t>purchase.order</t>
+        </is>
+      </c>
+      <c r="C27" s="7" t="inlineStr">
+        <is>
+          <t>Purchase Order</t>
+        </is>
+      </c>
+      <c r="D27" s="7" t="inlineStr">
+        <is>
+          <t>採購訂單</t>
+        </is>
+      </c>
+      <c r="E27" s="7" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>採購</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="inlineStr">
+        <is>
+          <t>purchase.order.line</t>
+        </is>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>Purchase Order Line</t>
+        </is>
+      </c>
+      <c r="D28" s="5" t="inlineStr">
+        <is>
+          <t>採購訂單項目</t>
+        </is>
+      </c>
+      <c r="E28" s="5" t="n">
+        <v>14</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:D25"/>
+  <autoFilter ref="A1:E28"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -4931,14 +6971,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E13"/>
+  <dimension ref="A1:E16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="44" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="46" customWidth="1" min="2" max="2"/>
+    <col width="32" customWidth="1" min="3" max="3"/>
     <col width="44" customWidth="1" min="4" max="4"/>
-    <col width="46" customWidth="1" min="5" max="5"/>
+    <col width="48" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5025,135 +7065,135 @@
     <row r="4" ht="32" customHeight="1">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>🔴 語意可疑</t>
+          <t>🔴 語意錯</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>res.partner.group_on</t>
+          <t>purchase.order.name</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>平日</t>
+          <t>訂單關聯</t>
         </is>
       </c>
       <c r="D4" s="6" t="inlineStr">
         <is>
-          <t>en 為 Week Day，採購分組語境下語意不明</t>
+          <t>en 為 Order Reference，此處 Reference 是單號不是關聯</t>
         </is>
       </c>
       <c r="E4" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>同一個 en 用在 purchase.order.line.order_id 時「訂單關聯」才正確</t>
         </is>
       </c>
     </row>
     <row r="5" ht="32" customHeight="1">
       <c r="A5" s="7" t="inlineStr">
         <is>
-          <t>⚠ 語意不足</t>
+          <t>🔴 語意可疑</t>
         </is>
       </c>
       <c r="B5" s="7" t="inlineStr">
         <is>
-          <t>res.partner.is_company</t>
+          <t>res.partner.group_on</t>
         </is>
       </c>
       <c r="C5" s="7" t="inlineStr">
         <is>
-          <t>公司</t>
+          <t>平日</t>
         </is>
       </c>
       <c r="D5" s="8" t="inlineStr">
         <is>
-          <t>布林欄位漏掉「是否為」，且與 company_id 的「公司」撞名</t>
+          <t>en 為 Week Day，採購分組語境下語意不明</t>
         </is>
       </c>
       <c r="E5" s="8" t="inlineStr">
         <is>
-          <t>res.partner.company_id 亦譯「公司」</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="6" ht="32" customHeight="1">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>⚠ 直譯誤導</t>
+          <t>⚠ 語意不足</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>res.partner.city_id</t>
+          <t>res.partner.is_company</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>城市識別碼</t>
+          <t>公司</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>many2one 關聯欄位，非識別碼；en 的 City ID 本身即誤導</t>
+          <t>布林欄位漏掉「是否為」，且與 company_id 的「公司」撞名</t>
         </is>
       </c>
       <c r="E6" s="6" t="inlineStr">
         <is>
-          <t>res.city.name 譯「名稱」</t>
+          <t>res.partner.company_id 亦譯「公司」</t>
         </is>
       </c>
     </row>
     <row r="7" ht="32" customHeight="1">
       <c r="A7" s="7" t="inlineStr">
         <is>
-          <t>⚠ 不一致</t>
+          <t>⚠ 直譯誤導</t>
         </is>
       </c>
       <c r="B7" s="7" t="inlineStr">
         <is>
-          <t>customer_rank / supplier_rank</t>
+          <t>res.partner.city_id</t>
         </is>
       </c>
       <c r="C7" s="7" t="inlineStr">
         <is>
-          <t>客戶評級 / 供應商排名</t>
+          <t>城市識別碼</t>
         </is>
       </c>
       <c r="D7" s="8" t="inlineStr">
         <is>
-          <t>同構欄位兩種譯法</t>
+          <t>many2one 關聯欄位，非識別碼；en 的 City ID 本身即誤導</t>
         </is>
       </c>
       <c r="E7" s="8" t="inlineStr">
         <is>
-          <t>同屬 res.partner</t>
+          <t>res.city.name 譯「名稱」</t>
         </is>
       </c>
     </row>
     <row r="8" ht="32" customHeight="1">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>⚠ 不一致</t>
+          <t>⚠ 直譯誤導</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>property_payment_term_id</t>
+          <t>purchase.order.partner_ref</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>客戶支付條款</t>
+          <t>供應商編碼</t>
         </is>
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>同一概念在 model 層譯法不同</t>
+          <t>en 為 Vendor Reference，指對方的單號而非編碼</t>
         </is>
       </c>
       <c r="E8" s="6" t="inlineStr">
         <is>
-          <t>account.payment.term.name 譯「付款條件」</t>
+          <t>purchase.order.name 同為 Reference 卻譯「關聯」</t>
         </is>
       </c>
     </row>
@@ -5165,22 +7205,22 @@
       </c>
       <c r="B9" s="7" t="inlineStr">
         <is>
-          <t>res.company.partner_id / res.users.partner_id</t>
+          <t>customer_rank / supplier_rank</t>
         </is>
       </c>
       <c r="C9" s="7" t="inlineStr">
         <is>
-          <t>業務夥伴 / 相關的合作夥伴</t>
+          <t>客戶評級 / 供應商排名</t>
         </is>
       </c>
       <c r="D9" s="8" t="inlineStr">
         <is>
-          <t>同一目標 model 兩種譯名</t>
+          <t>同構欄位兩種譯法</t>
         </is>
       </c>
       <c r="E9" s="8" t="inlineStr">
         <is>
-          <t>兩者 relation 皆為 res.partner</t>
+          <t>同屬 res.partner</t>
         </is>
       </c>
     </row>
@@ -5192,108 +7232,189 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>product.template.attribute.line / .value</t>
+          <t>property_payment_term_id</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>產品範本屬性資料行 / 產品模板屬性值</t>
+          <t>客戶支付條款</t>
         </is>
       </c>
       <c r="D10" s="6" t="inlineStr">
         <is>
-          <t>範本／模板混用</t>
+          <t>同一概念在 model 層譯法不同</t>
         </is>
       </c>
       <c r="E10" s="6" t="inlineStr">
         <is>
-          <t>ir_model.name 實查</t>
+          <t>account.payment.term.name 與 purchase.order.payment_term_id 皆譯「付款條件」</t>
         </is>
       </c>
     </row>
     <row r="11" ht="32" customHeight="1">
       <c r="A11" s="7" t="inlineStr">
         <is>
-          <t>⚠ 中國用字</t>
+          <t>⚠ 不一致</t>
         </is>
       </c>
       <c r="B11" s="7" t="inlineStr">
         <is>
-          <t>autopost_bills、property_account_receivable_id、property_account_payable_id</t>
+          <t>partner_id 的三種譯法</t>
         </is>
       </c>
       <c r="C11" s="7" t="inlineStr">
         <is>
-          <t>自動過賬賬單、應收賬戶、應付賬戶</t>
+          <t>業務夥伴 / 相關的合作夥伴 / 供應商</t>
         </is>
       </c>
       <c r="D11" s="8" t="inlineStr">
         <is>
-          <t>「賬」為中國用字，台灣作「帳」；且與圖上既有備註「應收科目／應付科目」衝突</t>
+          <t>同一目標 model 三種譯名</t>
         </is>
       </c>
       <c r="E11" s="8" t="inlineStr">
         <is>
-          <t>圖上 index.html 備註欄</t>
+          <t>res.company / res.users / purchase.order 皆指向 res.partner</t>
         </is>
       </c>
     </row>
     <row r="12" ht="32" customHeight="1">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>（缺）</t>
+          <t>⚠ 不一致</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>res.partner.group_rfq</t>
+          <t>product.template.attribute.line / .value</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>（無）</t>
+          <t>產品範本屬性資料行 / 產品模板屬性值</t>
         </is>
       </c>
       <c r="D12" s="6" t="inlineStr">
         <is>
-          <t>官方無 zh_TW 翻譯</t>
+          <t>範本／模板混用</t>
         </is>
       </c>
       <c r="E12" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>ir_model.name 實查</t>
         </is>
       </c>
     </row>
     <row r="13" ht="32" customHeight="1">
       <c r="A13" s="7" t="inlineStr">
         <is>
+          <t>⚠ 中國用字</t>
+        </is>
+      </c>
+      <c r="B13" s="7" t="inlineStr">
+        <is>
+          <t>autopost_bills、property_account_receivable_id、property_account_payable_id</t>
+        </is>
+      </c>
+      <c r="C13" s="7" t="inlineStr">
+        <is>
+          <t>自動過賬賬單、應收賬戶、應付賬戶</t>
+        </is>
+      </c>
+      <c r="D13" s="8" t="inlineStr">
+        <is>
+          <t>「賬」為中國用字，台灣作「帳」；與圖上既有備註「應收科目／應付科目」衝突</t>
+        </is>
+      </c>
+      <c r="E13" s="8" t="inlineStr">
+        <is>
+          <t>圖上 index.html 備註欄</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="32" customHeight="1">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
           <t>（缺）</t>
         </is>
       </c>
-      <c r="B13" s="7" t="inlineStr">
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>res.partner.group_rfq</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>（無）</t>
+        </is>
+      </c>
+      <c r="D14" s="6" t="inlineStr">
+        <is>
+          <t>官方無 zh_TW 翻譯</t>
+        </is>
+      </c>
+      <c r="E14" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="32" customHeight="1">
+      <c r="A15" s="7" t="inlineStr">
+        <is>
+          <t>（缺）</t>
+        </is>
+      </c>
+      <c r="B15" s="7" t="inlineStr">
         <is>
           <t>res.partner.bank.l10n_us_bank_account_type</t>
         </is>
       </c>
-      <c r="C13" s="7" t="inlineStr">
+      <c r="C15" s="7" t="inlineStr">
         <is>
           <t>（無）</t>
         </is>
       </c>
-      <c r="D13" s="8" t="inlineStr">
+      <c r="D15" s="8" t="inlineStr">
         <is>
           <t>官方無 zh_TW 翻譯</t>
         </is>
       </c>
-      <c r="E13" s="8" t="inlineStr">
+      <c r="E15" s="8" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
+    <row r="16" ht="32" customHeight="1">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>（缺）</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>purchase.order.line.display_type 的 line_subsection</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>（無）</t>
+        </is>
+      </c>
+      <c r="D16" s="6" t="inlineStr">
+        <is>
+          <t>selection 值缺 zh_TW，UI 會顯示英文</t>
+        </is>
+      </c>
+      <c r="E16" s="6" t="inlineStr">
+        <is>
+          <t>同欄位的 line_section 譯「章節」、line_note 譯「備註」</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E13"/>
+  <autoFilter ref="A1:E16"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>